--- a/outline_prediction_comparison.xlsx
+++ b/outline_prediction_comparison.xlsx
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H2">
         <v>0.08</v>
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="V2">
-        <v>0.23</v>
+        <v>1</v>
       </c>
       <c r="W2">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="H3">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -725,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="V3">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -775,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H4">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="V4">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="W4">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="V5">
-        <v>0.31</v>
+        <v>1</v>
       </c>
       <c r="W5">
         <v>0</v>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="V6">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="W6">
         <v>0</v>
@@ -1060,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="H7">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1105,10 +1105,10 @@
         <v>0</v>
       </c>
       <c r="V7">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X7">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="V8">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1295,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="V9">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>0</v>
       </c>
       <c r="V10">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="H11">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="V11">
-        <v>0.32</v>
+        <v>1</v>
       </c>
       <c r="W11">
         <v>0</v>
@@ -1535,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H12">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="V12">
-        <v>0.49</v>
+        <v>1</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -1630,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H13">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="V13">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -1725,10 +1725,10 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H14">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="V14">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="W14">
         <v>0</v>
@@ -1820,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="H15">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V15">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="W15">
         <v>0</v>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="V16">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="W16">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="V17">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="W17">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="H18">
         <v>0.04</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="V18">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="V19">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="W19">
         <v>0</v>
@@ -2295,10 +2295,10 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="H20">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="V20">
-        <v>0.36</v>
+        <v>1</v>
       </c>
       <c r="W20">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="H21">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="V21">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -2485,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2580,10 +2580,10 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="H23">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H24">
         <v>0.02</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="W24">
         <v>0</v>
@@ -2770,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="H25">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="V25">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -2865,10 +2865,10 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="H26">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2910,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="V26">
-        <v>0.25</v>
+        <v>0.84</v>
       </c>
       <c r="W26">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="X26">
         <v>0</v>
@@ -2960,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="H27">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="V27">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="W27">
         <v>0</v>
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H28">
         <v>0.06</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>0.34</v>
+        <v>0.99</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X28">
         <v>0</v>
@@ -3150,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="H29">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3195,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="V29">
-        <v>0.31</v>
+        <v>0.97</v>
       </c>
       <c r="W29">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X29">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="V30">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="V31">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="H32">
         <v>0.01</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="V32">
-        <v>0.34</v>
+        <v>0.99</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="H33">
         <v>0.02</v>
@@ -3575,10 +3575,10 @@
         <v>0</v>
       </c>
       <c r="V33">
-        <v>0.28</v>
+        <v>0.99</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X33">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H35">
         <v>0.05</v>
@@ -3765,10 +3765,10 @@
         <v>0</v>
       </c>
       <c r="V35">
-        <v>0.22</v>
+        <v>0.95</v>
       </c>
       <c r="W35">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="X35">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="V36">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="H37">
         <v>0.01</v>
@@ -3955,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="V37">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="W37">
         <v>0</v>
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="H38">
         <v>0.04</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="V38">
-        <v>0.27</v>
+        <v>0.96</v>
       </c>
       <c r="W38">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X38">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="V39">
-        <v>0.18</v>
+        <v>0.96</v>
       </c>
       <c r="W39">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H40">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4240,10 +4240,10 @@
         <v>0</v>
       </c>
       <c r="V40">
-        <v>0.21</v>
+        <v>0.97</v>
       </c>
       <c r="W40">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X40">
         <v>0</v>
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="H41">
         <v>0.04</v>
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="V41">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -4385,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="H42">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4430,10 +4430,10 @@
         <v>0</v>
       </c>
       <c r="V42">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X42">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -4525,10 +4525,10 @@
         <v>0</v>
       </c>
       <c r="V43">
-        <v>0.35</v>
+        <v>0.95</v>
       </c>
       <c r="W43">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="X43">
         <v>0</v>
@@ -4575,10 +4575,10 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="H44">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4620,10 +4620,10 @@
         <v>0</v>
       </c>
       <c r="V44">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X44">
         <v>0</v>
@@ -4670,10 +4670,10 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="H45">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="V45">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H46">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4810,10 +4810,10 @@
         <v>0</v>
       </c>
       <c r="V46">
-        <v>0.28</v>
+        <v>0.99</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -4860,10 +4860,10 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>0.78</v>
+        <v>0.89</v>
       </c>
       <c r="H47">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="V47">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="W47">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H48">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5000,10 +5000,10 @@
         <v>0</v>
       </c>
       <c r="V48">
-        <v>0.26</v>
+        <v>0.99</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -5050,10 +5050,10 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H49">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5095,10 +5095,10 @@
         <v>0</v>
       </c>
       <c r="V49">
-        <v>0.23</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W49">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="X49">
         <v>0</v>
@@ -5145,10 +5145,10 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H50">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="V50">
-        <v>0.29</v>
+        <v>0.99</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -5240,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H51">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5285,10 +5285,10 @@
         <v>0</v>
       </c>
       <c r="V51">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X51">
         <v>0</v>
@@ -5335,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="V52">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="H54">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5570,10 +5570,10 @@
         <v>0</v>
       </c>
       <c r="V54">
-        <v>0.32</v>
+        <v>0.99</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X54">
         <v>0</v>
@@ -5620,10 +5620,10 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="H55">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="H56">
         <v>0.01</v>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="V56">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="W56">
         <v>0</v>
@@ -5810,10 +5810,10 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="H57">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5855,10 +5855,10 @@
         <v>0</v>
       </c>
       <c r="V57">
-        <v>0.29</v>
+        <v>0.96</v>
       </c>
       <c r="W57">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X57">
         <v>0</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="H58">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -6000,10 +6000,10 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="H59">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6045,10 +6045,10 @@
         <v>0</v>
       </c>
       <c r="V59">
-        <v>0.21</v>
+        <v>0.99</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X59">
         <v>0</v>
@@ -6095,10 +6095,10 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="H60">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="V60">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="W60">
-        <v>0.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="X60">
         <v>0</v>
@@ -6190,10 +6190,10 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H61">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6235,10 +6235,10 @@
         <v>0</v>
       </c>
       <c r="V61">
-        <v>0.07000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -6285,10 +6285,10 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H62">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6330,10 +6330,10 @@
         <v>0</v>
       </c>
       <c r="V62">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="W62">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -6380,10 +6380,10 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H63">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6425,10 +6425,10 @@
         <v>0</v>
       </c>
       <c r="V63">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="W63">
-        <v>0.22</v>
+        <v>0.9</v>
       </c>
       <c r="X63">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="H64">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6520,10 +6520,10 @@
         <v>0</v>
       </c>
       <c r="V64">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="W64">
-        <v>0.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X64">
         <v>0</v>
@@ -6665,10 +6665,10 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="H66">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6710,10 +6710,10 @@
         <v>0</v>
       </c>
       <c r="V66">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.17</v>
+        <v>0.76</v>
       </c>
       <c r="X66">
         <v>0</v>
@@ -6760,10 +6760,10 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H67">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6805,10 +6805,10 @@
         <v>0</v>
       </c>
       <c r="V67">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W67">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="X67">
         <v>0</v>
@@ -6855,10 +6855,10 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H68">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="V68">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="W68">
-        <v>0.19</v>
+        <v>0.83</v>
       </c>
       <c r="X68">
         <v>0</v>
@@ -6950,10 +6950,10 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H69">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="V69">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="W69">
-        <v>0.23</v>
+        <v>0.9</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -7045,10 +7045,10 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H70">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -7090,10 +7090,10 @@
         <v>0</v>
       </c>
       <c r="V70">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="W70">
-        <v>0.15</v>
+        <v>0.66</v>
       </c>
       <c r="X70">
         <v>0</v>
@@ -7140,10 +7140,10 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="H71">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -7185,10 +7185,10 @@
         <v>0</v>
       </c>
       <c r="V71">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="W71">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="X71">
         <v>0</v>
@@ -7235,10 +7235,10 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="H72">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7280,10 +7280,10 @@
         <v>0</v>
       </c>
       <c r="V72">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="W72">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="X72">
         <v>0</v>
@@ -7330,10 +7330,10 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H73">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7375,10 +7375,10 @@
         <v>0</v>
       </c>
       <c r="V73">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="W73">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="X73">
         <v>0</v>
@@ -7425,10 +7425,10 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H74">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7470,10 +7470,10 @@
         <v>0</v>
       </c>
       <c r="V74">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="W74">
-        <v>0.16</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X74">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H75">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7565,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="V75">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="W75">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="X75">
         <v>0</v>
@@ -7615,10 +7615,10 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H76">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7660,10 +7660,10 @@
         <v>0</v>
       </c>
       <c r="V76">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="W76">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X76">
         <v>0</v>
@@ -7710,10 +7710,10 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="H77">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7755,10 +7755,10 @@
         <v>0</v>
       </c>
       <c r="V77">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="X77">
         <v>0</v>
@@ -7805,10 +7805,10 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H78">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7900,10 +7900,10 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="H79">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7995,10 +7995,10 @@
         <v>0</v>
       </c>
       <c r="G80">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="H80">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -8040,10 +8040,10 @@
         <v>0</v>
       </c>
       <c r="V80">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="W80">
-        <v>0.16</v>
+        <v>0.61</v>
       </c>
       <c r="X80">
         <v>0</v>
@@ -8090,10 +8090,10 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H81">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="V81">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="W81">
-        <v>0.14</v>
+        <v>0.71</v>
       </c>
       <c r="X81">
         <v>0</v>
@@ -8185,10 +8185,10 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="H82">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -8230,10 +8230,10 @@
         <v>0</v>
       </c>
       <c r="V82">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="W82">
-        <v>0.11</v>
+        <v>0.52</v>
       </c>
       <c r="X82">
         <v>0</v>
@@ -8280,10 +8280,10 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="H83">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="V83">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="W83">
-        <v>0.18</v>
+        <v>0.83</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -8375,10 +8375,10 @@
         <v>0</v>
       </c>
       <c r="G84">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H84">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -8420,10 +8420,10 @@
         <v>0</v>
       </c>
       <c r="V84">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="W84">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -8470,10 +8470,10 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H85">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -8515,10 +8515,10 @@
         <v>0</v>
       </c>
       <c r="V85">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="W85">
-        <v>0.13</v>
+        <v>0.62</v>
       </c>
       <c r="X85">
         <v>0</v>
@@ -8565,10 +8565,10 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="H86">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -8660,10 +8660,10 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H87">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="V87">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="W87">
-        <v>0.11</v>
+        <v>0.52</v>
       </c>
       <c r="X87">
         <v>0</v>
@@ -8755,10 +8755,10 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H88">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -8800,10 +8800,10 @@
         <v>0</v>
       </c>
       <c r="V88">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="W88">
-        <v>0.14</v>
+        <v>0.67</v>
       </c>
       <c r="X88">
         <v>0</v>
@@ -8850,10 +8850,10 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="H89">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -8895,10 +8895,10 @@
         <v>0</v>
       </c>
       <c r="V89">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="W89">
-        <v>0.08</v>
+        <v>0.46</v>
       </c>
       <c r="X89">
         <v>0</v>
@@ -8945,10 +8945,10 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="H90">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -8990,10 +8990,10 @@
         <v>0</v>
       </c>
       <c r="V90">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="W90">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="X90">
         <v>0</v>
@@ -9040,10 +9040,10 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="H91">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -9135,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="H92">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -9180,10 +9180,10 @@
         <v>0</v>
       </c>
       <c r="V92">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="W92">
-        <v>0.15</v>
+        <v>0.77</v>
       </c>
       <c r="X92">
         <v>0</v>
@@ -9230,10 +9230,10 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H93">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -9275,10 +9275,10 @@
         <v>0</v>
       </c>
       <c r="V93">
-        <v>0.07000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="W93">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -9328,7 +9328,7 @@
         <v>0.01</v>
       </c>
       <c r="H94">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -9370,10 +9370,10 @@
         <v>0</v>
       </c>
       <c r="V94">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="W94">
-        <v>0.15</v>
+        <v>0.68</v>
       </c>
       <c r="X94">
         <v>0</v>
@@ -9420,10 +9420,10 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H95">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -9465,10 +9465,10 @@
         <v>0</v>
       </c>
       <c r="V95">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="W95">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="X95">
         <v>0</v>
@@ -9515,10 +9515,10 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="H96">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -9560,10 +9560,10 @@
         <v>0</v>
       </c>
       <c r="V96">
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
       <c r="W96">
-        <v>0.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -9610,10 +9610,10 @@
         <v>0</v>
       </c>
       <c r="G97">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H97">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -9655,10 +9655,10 @@
         <v>0</v>
       </c>
       <c r="V97">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="W97">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="X97">
         <v>0</v>
@@ -9705,10 +9705,10 @@
         <v>0</v>
       </c>
       <c r="G98">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="H98">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -9750,10 +9750,10 @@
         <v>0</v>
       </c>
       <c r="V98">
-        <v>0.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W98">
-        <v>0.09</v>
+        <v>0.31</v>
       </c>
       <c r="X98">
         <v>0</v>
@@ -9800,10 +9800,10 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H99">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -9845,10 +9845,10 @@
         <v>0</v>
       </c>
       <c r="V99">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="W99">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="X99">
         <v>0</v>
@@ -9895,10 +9895,10 @@
         <v>0</v>
       </c>
       <c r="G100">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="H100">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -9940,10 +9940,10 @@
         <v>0</v>
       </c>
       <c r="V100">
-        <v>0.12</v>
+        <v>0.49</v>
       </c>
       <c r="W100">
-        <v>0.13</v>
+        <v>0.51</v>
       </c>
       <c r="X100">
         <v>0</v>
@@ -9990,10 +9990,10 @@
         <v>0</v>
       </c>
       <c r="G101">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="H101">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -10035,10 +10035,10 @@
         <v>0</v>
       </c>
       <c r="V101">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="W101">
-        <v>0.2</v>
+        <v>0.84</v>
       </c>
       <c r="X101">
         <v>0</v>
@@ -10085,10 +10085,10 @@
         <v>0</v>
       </c>
       <c r="G102">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="H102">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -10180,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="G103">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H103">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="I103">
         <v>0</v>
@@ -10225,10 +10225,10 @@
         <v>0</v>
       </c>
       <c r="V103">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="W103">
-        <v>0.07000000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="X103">
         <v>0</v>
@@ -10275,10 +10275,10 @@
         <v>0</v>
       </c>
       <c r="G104">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H104">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -10320,10 +10320,10 @@
         <v>0</v>
       </c>
       <c r="V104">
-        <v>0.14</v>
+        <v>0.71</v>
       </c>
       <c r="W104">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="X104">
         <v>0</v>
@@ -10370,10 +10370,10 @@
         <v>0</v>
       </c>
       <c r="G105">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H105">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -10415,10 +10415,10 @@
         <v>0</v>
       </c>
       <c r="V105">
-        <v>0.18</v>
+        <v>0.89</v>
       </c>
       <c r="W105">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="X105">
         <v>0</v>
@@ -10465,10 +10465,10 @@
         <v>0</v>
       </c>
       <c r="G106">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="H106">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -10510,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="V106">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="W106">
         <v>0</v>
@@ -10560,10 +10560,10 @@
         <v>0</v>
       </c>
       <c r="G107">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H107">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -10605,10 +10605,10 @@
         <v>0</v>
       </c>
       <c r="V107">
-        <v>0.22</v>
+        <v>0.93</v>
       </c>
       <c r="W107">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X107">
         <v>0</v>
@@ -10655,10 +10655,10 @@
         <v>0</v>
       </c>
       <c r="G108">
-        <v>0.59</v>
+        <v>0.91</v>
       </c>
       <c r="H108">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -10700,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="V108">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="W108">
         <v>0</v>
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="G109">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="H109">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -10795,10 +10795,10 @@
         <v>0</v>
       </c>
       <c r="V109">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X109">
         <v>0</v>
@@ -10845,10 +10845,10 @@
         <v>0</v>
       </c>
       <c r="G110">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="H110">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -10890,7 +10890,7 @@
         <v>0</v>
       </c>
       <c r="V110">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="W110">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="H111">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -10985,10 +10985,10 @@
         <v>0</v>
       </c>
       <c r="V111">
-        <v>0.21</v>
+        <v>0.96</v>
       </c>
       <c r="W111">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X111">
         <v>0</v>
@@ -11035,10 +11035,10 @@
         <v>0</v>
       </c>
       <c r="G112">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="H112">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
       <c r="V112">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W112">
         <v>0</v>
@@ -11130,10 +11130,10 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H113">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -11175,10 +11175,10 @@
         <v>0</v>
       </c>
       <c r="V113">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X113">
         <v>0</v>
@@ -11225,10 +11225,10 @@
         <v>0</v>
       </c>
       <c r="G114">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="H114">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -11270,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="V114">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="W114">
-        <v>0.19</v>
+        <v>0.72</v>
       </c>
       <c r="X114">
         <v>0</v>
@@ -11320,10 +11320,10 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H115">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -11365,10 +11365,10 @@
         <v>0</v>
       </c>
       <c r="V115">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="W115">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="X115">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="G116">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="H116">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -11460,10 +11460,10 @@
         <v>0</v>
       </c>
       <c r="V116">
-        <v>0.11</v>
+        <v>0.42</v>
       </c>
       <c r="W116">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="X116">
         <v>0</v>
@@ -11555,10 +11555,10 @@
         <v>0</v>
       </c>
       <c r="V117">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="W117">
-        <v>0.24</v>
+        <v>0.97</v>
       </c>
       <c r="X117">
         <v>0</v>
@@ -11605,10 +11605,10 @@
         <v>0</v>
       </c>
       <c r="G118">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H118">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -11650,10 +11650,10 @@
         <v>0</v>
       </c>
       <c r="V118">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="W118">
-        <v>0.22</v>
+        <v>0.86</v>
       </c>
       <c r="X118">
         <v>0</v>
@@ -11700,10 +11700,10 @@
         <v>0</v>
       </c>
       <c r="G119">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="H119">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -11745,10 +11745,10 @@
         <v>0</v>
       </c>
       <c r="V119">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="W119">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
       <c r="X119">
         <v>0</v>
@@ -11795,10 +11795,10 @@
         <v>0</v>
       </c>
       <c r="G120">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H120">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="G121">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H121">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -11935,10 +11935,10 @@
         <v>0</v>
       </c>
       <c r="V121">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="W121">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="X121">
         <v>0</v>
@@ -11985,10 +11985,10 @@
         <v>0</v>
       </c>
       <c r="G122">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="H122">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -12030,10 +12030,10 @@
         <v>0</v>
       </c>
       <c r="V122">
-        <v>0.18</v>
+        <v>0.83</v>
       </c>
       <c r="W122">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="X122">
         <v>0</v>
@@ -12080,10 +12080,10 @@
         <v>0</v>
       </c>
       <c r="G123">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="H123">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -12125,10 +12125,10 @@
         <v>0</v>
       </c>
       <c r="V123">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="W123">
-        <v>0.13</v>
+        <v>0.61</v>
       </c>
       <c r="X123">
         <v>0</v>
@@ -12175,10 +12175,10 @@
         <v>0</v>
       </c>
       <c r="G124">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="H124">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -12220,10 +12220,10 @@
         <v>0</v>
       </c>
       <c r="V124">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="W124">
-        <v>0.17</v>
+        <v>0.88</v>
       </c>
       <c r="X124">
         <v>0</v>
@@ -12270,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="G125">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H125">
         <v>0.02</v>
@@ -12365,7 +12365,7 @@
         <v>0</v>
       </c>
       <c r="G126">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="V126">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="W126">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="X126">
         <v>0</v>
@@ -12460,7 +12460,7 @@
         <v>0</v>
       </c>
       <c r="G127">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -12505,10 +12505,10 @@
         <v>0</v>
       </c>
       <c r="V127">
-        <v>0.07000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="W127">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="X127">
         <v>0</v>
@@ -12555,7 +12555,7 @@
         <v>0</v>
       </c>
       <c r="G128">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -12600,10 +12600,10 @@
         <v>0</v>
       </c>
       <c r="V128">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="W128">
-        <v>0.12</v>
+        <v>0.55</v>
       </c>
       <c r="X128">
         <v>0</v>
@@ -12650,10 +12650,10 @@
         <v>0</v>
       </c>
       <c r="G129">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H129">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -12695,10 +12695,10 @@
         <v>0</v>
       </c>
       <c r="V129">
-        <v>0.03</v>
+        <v>0.21</v>
       </c>
       <c r="W129">
-        <v>0.12</v>
+        <v>0.79</v>
       </c>
       <c r="X129">
         <v>0</v>
@@ -12745,10 +12745,10 @@
         <v>0</v>
       </c>
       <c r="G130">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H130">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -12790,10 +12790,10 @@
         <v>0</v>
       </c>
       <c r="V130">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="W130">
-        <v>0.14</v>
+        <v>0.78</v>
       </c>
       <c r="X130">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="G131">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H131">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -12935,10 +12935,10 @@
         <v>0</v>
       </c>
       <c r="G132">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="H132">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -12980,10 +12980,10 @@
         <v>0</v>
       </c>
       <c r="V132">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="W132">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="X132">
         <v>0</v>
@@ -13030,10 +13030,10 @@
         <v>0</v>
       </c>
       <c r="G133">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H133">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -13075,10 +13075,10 @@
         <v>0</v>
       </c>
       <c r="V133">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="W133">
-        <v>0.19</v>
+        <v>0.96</v>
       </c>
       <c r="X133">
         <v>0</v>
@@ -13125,10 +13125,10 @@
         <v>0</v>
       </c>
       <c r="G134">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H134">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -13170,10 +13170,10 @@
         <v>0</v>
       </c>
       <c r="V134">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="W134">
-        <v>0.12</v>
+        <v>0.88</v>
       </c>
       <c r="X134">
         <v>0</v>
@@ -13220,10 +13220,10 @@
         <v>0</v>
       </c>
       <c r="G135">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H135">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -13265,10 +13265,10 @@
         <v>0</v>
       </c>
       <c r="V135">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="W135">
-        <v>0.18</v>
+        <v>0.91</v>
       </c>
       <c r="X135">
         <v>0</v>
@@ -13315,10 +13315,10 @@
         <v>0</v>
       </c>
       <c r="G136">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H136">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -13360,10 +13360,10 @@
         <v>0</v>
       </c>
       <c r="V136">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="W136">
-        <v>0.15</v>
+        <v>0.92</v>
       </c>
       <c r="X136">
         <v>0</v>
@@ -13410,10 +13410,10 @@
         <v>0</v>
       </c>
       <c r="G137">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="H137">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -13455,10 +13455,10 @@
         <v>0</v>
       </c>
       <c r="V137">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="W137">
-        <v>0.13</v>
+        <v>0.73</v>
       </c>
       <c r="X137">
         <v>0</v>
@@ -13505,10 +13505,10 @@
         <v>0</v>
       </c>
       <c r="G138">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H138">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -13550,10 +13550,10 @@
         <v>0</v>
       </c>
       <c r="V138">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="W138">
-        <v>0.13</v>
+        <v>0.84</v>
       </c>
       <c r="X138">
         <v>0</v>
@@ -13600,10 +13600,10 @@
         <v>0</v>
       </c>
       <c r="G139">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H139">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -13645,10 +13645,10 @@
         <v>0</v>
       </c>
       <c r="V139">
-        <v>0.06</v>
+        <v>0.28</v>
       </c>
       <c r="W139">
-        <v>0.14</v>
+        <v>0.72</v>
       </c>
       <c r="X139">
         <v>0</v>
@@ -13695,10 +13695,10 @@
         <v>0</v>
       </c>
       <c r="G140">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H140">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -13740,10 +13740,10 @@
         <v>0</v>
       </c>
       <c r="V140">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="W140">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X140">
         <v>0</v>
@@ -13790,10 +13790,10 @@
         <v>0</v>
       </c>
       <c r="G141">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H141">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -13835,10 +13835,10 @@
         <v>0</v>
       </c>
       <c r="V141">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="W141">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="X141">
         <v>0</v>
@@ -13885,10 +13885,10 @@
         <v>0</v>
       </c>
       <c r="G142">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="H142">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -13930,10 +13930,10 @@
         <v>0</v>
       </c>
       <c r="V142">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="W142">
-        <v>0.18</v>
+        <v>0.73</v>
       </c>
       <c r="X142">
         <v>0</v>
@@ -13980,10 +13980,10 @@
         <v>0</v>
       </c>
       <c r="G143">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H143">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -14025,10 +14025,10 @@
         <v>0</v>
       </c>
       <c r="V143">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="W143">
-        <v>0.16</v>
+        <v>0.83</v>
       </c>
       <c r="X143">
         <v>0</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="G144">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="H144">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -14120,10 +14120,10 @@
         <v>0</v>
       </c>
       <c r="V144">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="W144">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="X144">
         <v>0</v>
@@ -14170,10 +14170,10 @@
         <v>0</v>
       </c>
       <c r="G145">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H145">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -14215,10 +14215,10 @@
         <v>0</v>
       </c>
       <c r="V145">
-        <v>0.07000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="W145">
-        <v>0.13</v>
+        <v>0.64</v>
       </c>
       <c r="X145">
         <v>0</v>
@@ -14265,10 +14265,10 @@
         <v>0</v>
       </c>
       <c r="G146">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="H146">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -14360,10 +14360,10 @@
         <v>0</v>
       </c>
       <c r="G147">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="H147">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -14405,10 +14405,10 @@
         <v>0</v>
       </c>
       <c r="V147">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="W147">
-        <v>0.14</v>
+        <v>0.77</v>
       </c>
       <c r="X147">
         <v>0</v>
@@ -14455,10 +14455,10 @@
         <v>0</v>
       </c>
       <c r="G148">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H148">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -14500,10 +14500,10 @@
         <v>0</v>
       </c>
       <c r="V148">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="W148">
-        <v>0.13</v>
+        <v>0.83</v>
       </c>
       <c r="X148">
         <v>0</v>
@@ -14553,7 +14553,7 @@
         <v>0</v>
       </c>
       <c r="H149">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -14595,10 +14595,10 @@
         <v>0</v>
       </c>
       <c r="V149">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="W149">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="X149">
         <v>0</v>
@@ -14645,10 +14645,10 @@
         <v>0</v>
       </c>
       <c r="G150">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H150">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -14690,10 +14690,10 @@
         <v>0</v>
       </c>
       <c r="V150">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="W150">
-        <v>0.14</v>
+        <v>0.85</v>
       </c>
       <c r="X150">
         <v>0</v>
@@ -14740,10 +14740,10 @@
         <v>0</v>
       </c>
       <c r="G151">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H151">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="I151">
         <v>0</v>
@@ -14785,10 +14785,10 @@
         <v>0</v>
       </c>
       <c r="V151">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="W151">
-        <v>0.21</v>
+        <v>0.74</v>
       </c>
       <c r="X151">
         <v>0</v>
@@ -14835,7 +14835,7 @@
         <v>0</v>
       </c>
       <c r="G152">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H152">
         <v>0</v>
@@ -14880,10 +14880,10 @@
         <v>0</v>
       </c>
       <c r="V152">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X152">
         <v>0</v>
@@ -14930,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G153">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H153">
         <v>0</v>
@@ -14975,10 +14975,10 @@
         <v>0</v>
       </c>
       <c r="V153">
-        <v>0.16</v>
+        <v>0.93</v>
       </c>
       <c r="W153">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X153">
         <v>0</v>
@@ -15025,10 +15025,10 @@
         <v>0</v>
       </c>
       <c r="G154">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="H154">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -15070,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="V154">
-        <v>0.26</v>
+        <v>0.96</v>
       </c>
       <c r="W154">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X154">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G155">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="H155">
         <v>0.05</v>
@@ -15165,10 +15165,10 @@
         <v>0</v>
       </c>
       <c r="V155">
-        <v>0.17</v>
+        <v>0.96</v>
       </c>
       <c r="W155">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X155">
         <v>0</v>
@@ -15215,10 +15215,10 @@
         <v>0</v>
       </c>
       <c r="G156">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="H156">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -15260,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="V156">
-        <v>0.19</v>
+        <v>0.97</v>
       </c>
       <c r="W156">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X156">
         <v>0</v>
@@ -15310,7 +15310,7 @@
         <v>0</v>
       </c>
       <c r="G157">
-        <v>0.83</v>
+        <v>0.99</v>
       </c>
       <c r="H157">
         <v>0.01</v>
@@ -15355,10 +15355,10 @@
         <v>0</v>
       </c>
       <c r="V157">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="W157">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="X157">
         <v>0</v>
@@ -15450,10 +15450,10 @@
         <v>0</v>
       </c>
       <c r="V158">
+        <v>0.84</v>
+      </c>
+      <c r="W158">
         <v>0.16</v>
-      </c>
-      <c r="W158">
-        <v>0.03</v>
       </c>
       <c r="X158">
         <v>0</v>
@@ -15500,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="G159">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H159">
         <v>0</v>
@@ -15595,10 +15595,10 @@
         <v>0</v>
       </c>
       <c r="G160">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="H160">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -15640,10 +15640,10 @@
         <v>0</v>
       </c>
       <c r="V160">
-        <v>0.16</v>
+        <v>0.83</v>
       </c>
       <c r="W160">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="X160">
         <v>0</v>
@@ -15690,7 +15690,7 @@
         <v>0</v>
       </c>
       <c r="G161">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H161">
         <v>0</v>
@@ -15735,10 +15735,10 @@
         <v>0</v>
       </c>
       <c r="V161">
-        <v>0.2</v>
+        <v>0.99</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X161">
         <v>0</v>
@@ -15785,7 +15785,7 @@
         <v>0</v>
       </c>
       <c r="G162">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H162">
         <v>0</v>
@@ -15830,10 +15830,10 @@
         <v>0</v>
       </c>
       <c r="V162">
-        <v>0.17</v>
+        <v>0.98</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X162">
         <v>0</v>
@@ -15880,7 +15880,7 @@
         <v>0</v>
       </c>
       <c r="G163">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="H163">
         <v>0</v>
@@ -15975,7 +15975,7 @@
         <v>0</v>
       </c>
       <c r="G164">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="H164">
         <v>0.04</v>
@@ -16020,10 +16020,10 @@
         <v>0</v>
       </c>
       <c r="V164">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X164">
         <v>0</v>
@@ -16070,7 +16070,7 @@
         <v>0</v>
       </c>
       <c r="G165">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="H165">
         <v>0.05</v>
@@ -16165,7 +16165,7 @@
         <v>0</v>
       </c>
       <c r="G166">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="H166">
         <v>0.04</v>
@@ -16210,10 +16210,10 @@
         <v>0</v>
       </c>
       <c r="V166">
-        <v>0.2</v>
+        <v>0.99</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X166">
         <v>0</v>
@@ -16260,10 +16260,10 @@
         <v>0</v>
       </c>
       <c r="G167">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="H167">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -16355,7 +16355,7 @@
         <v>0</v>
       </c>
       <c r="G168">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H168">
         <v>0</v>
@@ -16400,10 +16400,10 @@
         <v>0</v>
       </c>
       <c r="V168">
-        <v>0.18</v>
+        <v>0.83</v>
       </c>
       <c r="W168">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="X168">
         <v>0</v>
@@ -16545,7 +16545,7 @@
         <v>0</v>
       </c>
       <c r="G170">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H170">
         <v>0</v>
@@ -16590,7 +16590,7 @@
         <v>0</v>
       </c>
       <c r="V170">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="W170">
         <v>0</v>
@@ -16685,10 +16685,10 @@
         <v>0</v>
       </c>
       <c r="V171">
-        <v>0.15</v>
+        <v>0.99</v>
       </c>
       <c r="W171">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X171">
         <v>0</v>
@@ -16735,7 +16735,7 @@
         <v>0</v>
       </c>
       <c r="G172">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H172">
         <v>0</v>
@@ -16780,10 +16780,10 @@
         <v>0</v>
       </c>
       <c r="V172">
-        <v>0.29</v>
+        <v>0.99</v>
       </c>
       <c r="W172">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X172">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="G173">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H173">
         <v>0</v>
@@ -16875,10 +16875,10 @@
         <v>0</v>
       </c>
       <c r="V173">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W173">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X173">
         <v>0</v>
@@ -17020,7 +17020,7 @@
         <v>0</v>
       </c>
       <c r="G175">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="H175">
         <v>0</v>
@@ -17065,10 +17065,10 @@
         <v>0</v>
       </c>
       <c r="V175">
-        <v>0.23</v>
+        <v>0.99</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X175">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G176">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="H176">
         <v>0.04</v>
@@ -17160,10 +17160,10 @@
         <v>0</v>
       </c>
       <c r="V176">
-        <v>0.25</v>
+        <v>0.97</v>
       </c>
       <c r="W176">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X176">
         <v>0</v>
@@ -17210,7 +17210,7 @@
         <v>0</v>
       </c>
       <c r="G177">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -17255,10 +17255,10 @@
         <v>0</v>
       </c>
       <c r="V177">
-        <v>0.22</v>
+        <v>0.99</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X177">
         <v>0</v>
@@ -17350,10 +17350,10 @@
         <v>0</v>
       </c>
       <c r="V178">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
       <c r="W178">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="X178">
         <v>0</v>
@@ -17445,10 +17445,10 @@
         <v>0</v>
       </c>
       <c r="V179">
-        <v>0.22</v>
+        <v>0.98</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X179">
         <v>0</v>
@@ -17495,7 +17495,7 @@
         <v>0</v>
       </c>
       <c r="G180">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="H180">
         <v>0.05</v>
@@ -17540,10 +17540,10 @@
         <v>0</v>
       </c>
       <c r="V180">
-        <v>0.23</v>
+        <v>0.92</v>
       </c>
       <c r="W180">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="X180">
         <v>0</v>
@@ -17590,10 +17590,10 @@
         <v>0</v>
       </c>
       <c r="G181">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="H181">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -17635,10 +17635,10 @@
         <v>0</v>
       </c>
       <c r="V181">
-        <v>0.2</v>
+        <v>0.86</v>
       </c>
       <c r="W181">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="X181">
         <v>0</v>
@@ -17685,10 +17685,10 @@
         <v>0</v>
       </c>
       <c r="G182">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="H182">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -17730,10 +17730,10 @@
         <v>0</v>
       </c>
       <c r="V182">
-        <v>0.18</v>
+        <v>0.91</v>
       </c>
       <c r="W182">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="X182">
         <v>0</v>
@@ -17780,7 +17780,7 @@
         <v>0</v>
       </c>
       <c r="G183">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="H183">
         <v>0</v>
@@ -17875,7 +17875,7 @@
         <v>0</v>
       </c>
       <c r="G184">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="H184">
         <v>0</v>
@@ -17920,10 +17920,10 @@
         <v>0</v>
       </c>
       <c r="V184">
-        <v>0.23</v>
+        <v>0.96</v>
       </c>
       <c r="W184">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="X184">
         <v>0</v>
@@ -17970,7 +17970,7 @@
         <v>0</v>
       </c>
       <c r="G185">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="H185">
         <v>0.09</v>
@@ -18015,10 +18015,10 @@
         <v>0</v>
       </c>
       <c r="V185">
-        <v>0.23</v>
+        <v>0.98</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X185">
         <v>0</v>
@@ -18065,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="G186">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H186">
         <v>0.06</v>
@@ -18110,10 +18110,10 @@
         <v>0</v>
       </c>
       <c r="V186">
-        <v>0.21</v>
+        <v>0.98</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X186">
         <v>0</v>
@@ -18160,10 +18160,10 @@
         <v>0</v>
       </c>
       <c r="G187">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="H187">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -18205,10 +18205,10 @@
         <v>0</v>
       </c>
       <c r="V187">
-        <v>0.22</v>
+        <v>0.98</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="X187">
         <v>0</v>
@@ -18255,7 +18255,7 @@
         <v>0</v>
       </c>
       <c r="G188">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="H188">
         <v>0</v>
@@ -18300,10 +18300,10 @@
         <v>0</v>
       </c>
       <c r="V188">
-        <v>0.2</v>
+        <v>0.93</v>
       </c>
       <c r="W188">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X188">
         <v>0</v>
@@ -18350,7 +18350,7 @@
         <v>0</v>
       </c>
       <c r="G189">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="H189">
         <v>0</v>
@@ -18395,10 +18395,10 @@
         <v>0</v>
       </c>
       <c r="V189">
-        <v>0.26</v>
+        <v>0.99</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X189">
         <v>0</v>
@@ -18445,7 +18445,7 @@
         <v>0</v>
       </c>
       <c r="G190">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="H190">
         <v>0.02</v>
@@ -18490,10 +18490,10 @@
         <v>0</v>
       </c>
       <c r="V190">
-        <v>0.18</v>
+        <v>0.92</v>
       </c>
       <c r="W190">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="X190">
         <v>0</v>
@@ -18540,10 +18540,10 @@
         <v>0</v>
       </c>
       <c r="G191">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="H191">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I191">
         <v>0</v>
@@ -18585,10 +18585,10 @@
         <v>0</v>
       </c>
       <c r="V191">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
       <c r="W191">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="X191">
         <v>0</v>
@@ -18635,7 +18635,7 @@
         <v>0</v>
       </c>
       <c r="G192">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H192">
         <v>0</v>
@@ -18680,10 +18680,10 @@
         <v>0</v>
       </c>
       <c r="V192">
-        <v>0.19</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W192">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="X192">
         <v>0</v>
@@ -18775,10 +18775,10 @@
         <v>0</v>
       </c>
       <c r="V193">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="W193">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="X193">
         <v>0</v>
@@ -18825,7 +18825,7 @@
         <v>0</v>
       </c>
       <c r="G194">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="H194">
         <v>0.04</v>
@@ -18870,10 +18870,10 @@
         <v>0</v>
       </c>
       <c r="V194">
-        <v>0.2</v>
+        <v>0.99</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X194">
         <v>0</v>
@@ -19060,10 +19060,10 @@
         <v>0</v>
       </c>
       <c r="V196">
-        <v>0.18</v>
+        <v>0.86</v>
       </c>
       <c r="W196">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="X196">
         <v>0</v>
@@ -19110,7 +19110,7 @@
         <v>0</v>
       </c>
       <c r="G197">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="H197">
         <v>0.01</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="V197">
-        <v>0.18</v>
+        <v>0.97</v>
       </c>
       <c r="W197">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X197">
         <v>0</v>
@@ -19205,7 +19205,7 @@
         <v>0</v>
       </c>
       <c r="G198">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H198">
         <v>0</v>
@@ -19250,10 +19250,10 @@
         <v>0</v>
       </c>
       <c r="V198">
-        <v>0.31</v>
+        <v>0.98</v>
       </c>
       <c r="W198">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="X198">
         <v>0</v>
@@ -19300,7 +19300,7 @@
         <v>0</v>
       </c>
       <c r="G199">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H199">
         <v>0</v>
@@ -19395,10 +19395,10 @@
         <v>0</v>
       </c>
       <c r="G200">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="H200">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="I200">
         <v>0</v>
@@ -19440,10 +19440,10 @@
         <v>0</v>
       </c>
       <c r="V200">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X200">
         <v>0</v>
@@ -19490,7 +19490,7 @@
         <v>0</v>
       </c>
       <c r="G201">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H201">
         <v>0</v>
@@ -19535,7 +19535,7 @@
         <v>0</v>
       </c>
       <c r="V201">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="W201">
         <v>0</v>
@@ -19585,10 +19585,10 @@
         <v>0</v>
       </c>
       <c r="G202">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="H202">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I202">
         <v>0</v>
@@ -19630,10 +19630,10 @@
         <v>0</v>
       </c>
       <c r="V202">
-        <v>0.21</v>
+        <v>0.92</v>
       </c>
       <c r="W202">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="X202">
         <v>0</v>
@@ -19680,7 +19680,7 @@
         <v>0</v>
       </c>
       <c r="G203">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="H203">
         <v>0.08</v>
@@ -19725,10 +19725,10 @@
         <v>0</v>
       </c>
       <c r="V203">
-        <v>0.17</v>
+        <v>0.92</v>
       </c>
       <c r="W203">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="X203">
         <v>0</v>
@@ -19775,10 +19775,10 @@
         <v>0</v>
       </c>
       <c r="G204">
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
       <c r="H204">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I204">
         <v>0</v>
@@ -19820,10 +19820,10 @@
         <v>0</v>
       </c>
       <c r="V204">
-        <v>0.21</v>
+        <v>0.97</v>
       </c>
       <c r="W204">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X204">
         <v>0</v>
@@ -19870,7 +19870,7 @@
         <v>0</v>
       </c>
       <c r="G205">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H205">
         <v>0</v>
@@ -19915,10 +19915,10 @@
         <v>0</v>
       </c>
       <c r="V205">
-        <v>0.25</v>
+        <v>0.97</v>
       </c>
       <c r="W205">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X205">
         <v>0</v>
@@ -19965,7 +19965,7 @@
         <v>0</v>
       </c>
       <c r="G206">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H206">
         <v>0</v>
@@ -20010,10 +20010,10 @@
         <v>0</v>
       </c>
       <c r="V206">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X206">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>0</v>
       </c>
       <c r="G207">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H207">
         <v>0</v>
@@ -20105,10 +20105,10 @@
         <v>0</v>
       </c>
       <c r="V207">
-        <v>0.21</v>
+        <v>0.99</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X207">
         <v>0</v>
@@ -20203,7 +20203,7 @@
         <v>0</v>
       </c>
       <c r="W208">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="X208">
         <v>0</v>
@@ -20250,10 +20250,10 @@
         <v>0</v>
       </c>
       <c r="G209">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H209">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="I209">
         <v>0</v>
@@ -20295,10 +20295,10 @@
         <v>0</v>
       </c>
       <c r="V209">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="W209">
-        <v>0.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="X209">
         <v>0</v>
@@ -20345,10 +20345,10 @@
         <v>0</v>
       </c>
       <c r="G210">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H210">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="I210">
         <v>0</v>
@@ -20390,10 +20390,10 @@
         <v>0</v>
       </c>
       <c r="V210">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="W210">
-        <v>0.13</v>
+        <v>0.73</v>
       </c>
       <c r="X210">
         <v>0</v>
@@ -20440,10 +20440,10 @@
         <v>0</v>
       </c>
       <c r="G211">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H211">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="I211">
         <v>0</v>
@@ -20538,7 +20538,7 @@
         <v>0</v>
       </c>
       <c r="H212">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -20580,10 +20580,10 @@
         <v>0</v>
       </c>
       <c r="V212">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="W212">
-        <v>0.19</v>
+        <v>0.7</v>
       </c>
       <c r="X212">
         <v>0</v>
@@ -20630,10 +20630,10 @@
         <v>0</v>
       </c>
       <c r="G213">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H213">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -20675,10 +20675,10 @@
         <v>0</v>
       </c>
       <c r="V213">
-        <v>0.07000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="W213">
-        <v>0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="X213">
         <v>0</v>
@@ -20820,10 +20820,10 @@
         <v>0</v>
       </c>
       <c r="G215">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H215">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="I215">
         <v>0</v>
@@ -20915,10 +20915,10 @@
         <v>0</v>
       </c>
       <c r="G216">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H216">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="I216">
         <v>0</v>
@@ -20960,10 +20960,10 @@
         <v>0</v>
       </c>
       <c r="V216">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="W216">
-        <v>0.17</v>
+        <v>0.87</v>
       </c>
       <c r="X216">
         <v>0</v>
@@ -21010,10 +21010,10 @@
         <v>0</v>
       </c>
       <c r="G217">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="H217">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -21055,10 +21055,10 @@
         <v>0</v>
       </c>
       <c r="V217">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="W217">
-        <v>0.11</v>
+        <v>0.58</v>
       </c>
       <c r="X217">
         <v>0</v>
@@ -21108,7 +21108,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="H218">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="I218">
         <v>0</v>
@@ -21200,10 +21200,10 @@
         <v>0</v>
       </c>
       <c r="G219">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H219">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="I219">
         <v>0</v>
@@ -21245,10 +21245,10 @@
         <v>0</v>
       </c>
       <c r="V219">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="W219">
-        <v>0.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X219">
         <v>0</v>
@@ -21295,10 +21295,10 @@
         <v>0</v>
       </c>
       <c r="G220">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="H220">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="I220">
         <v>0</v>
@@ -21340,10 +21340,10 @@
         <v>0</v>
       </c>
       <c r="V220">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="W220">
-        <v>0.27</v>
+        <v>0.62</v>
       </c>
       <c r="X220">
         <v>0</v>
@@ -21390,10 +21390,10 @@
         <v>0</v>
       </c>
       <c r="G221">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H221">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="I221">
         <v>0</v>
@@ -21485,10 +21485,10 @@
         <v>0</v>
       </c>
       <c r="G222">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H222">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="I222">
         <v>0</v>
@@ -21530,10 +21530,10 @@
         <v>0</v>
       </c>
       <c r="V222">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="W222">
-        <v>0.12</v>
+        <v>0.71</v>
       </c>
       <c r="X222">
         <v>0</v>
@@ -21580,10 +21580,10 @@
         <v>0</v>
       </c>
       <c r="G223">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="H223">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="I223">
         <v>0</v>
@@ -21720,10 +21720,10 @@
         <v>0</v>
       </c>
       <c r="V224">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="W224">
-        <v>0.07000000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="X224">
         <v>0</v>
@@ -21770,10 +21770,10 @@
         <v>0</v>
       </c>
       <c r="G225">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H225">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="I225">
         <v>0</v>
@@ -21815,10 +21815,10 @@
         <v>0</v>
       </c>
       <c r="V225">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
       <c r="W225">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
       <c r="X225">
         <v>0</v>
@@ -21865,10 +21865,10 @@
         <v>0</v>
       </c>
       <c r="G226">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H226">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="I226">
         <v>0</v>
@@ -21910,10 +21910,10 @@
         <v>0</v>
       </c>
       <c r="V226">
-        <v>0.05</v>
+        <v>0.33</v>
       </c>
       <c r="W226">
-        <v>0.11</v>
+        <v>0.67</v>
       </c>
       <c r="X226">
         <v>0</v>
@@ -21960,10 +21960,10 @@
         <v>0</v>
       </c>
       <c r="G227">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H227">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="I227">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="V227">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="W227">
-        <v>0.14</v>
+        <v>0.71</v>
       </c>
       <c r="X227">
         <v>0</v>
@@ -22055,10 +22055,10 @@
         <v>0</v>
       </c>
       <c r="G228">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="H228">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -22150,10 +22150,10 @@
         <v>0</v>
       </c>
       <c r="G229">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H229">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="I229">
         <v>0</v>
@@ -22195,10 +22195,10 @@
         <v>0</v>
       </c>
       <c r="V229">
-        <v>0.05</v>
+        <v>0.28</v>
       </c>
       <c r="W229">
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="X229">
         <v>0</v>
@@ -22245,10 +22245,10 @@
         <v>0</v>
       </c>
       <c r="G230">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="H230">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="I230">
         <v>0</v>
@@ -22290,10 +22290,10 @@
         <v>0</v>
       </c>
       <c r="V230">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W230">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="X230">
         <v>0</v>
@@ -22340,10 +22340,10 @@
         <v>0</v>
       </c>
       <c r="G231">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H231">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I231">
         <v>0</v>
@@ -22435,10 +22435,10 @@
         <v>0</v>
       </c>
       <c r="G232">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="H232">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="I232">
         <v>0</v>
@@ -22480,10 +22480,10 @@
         <v>0</v>
       </c>
       <c r="V232">
-        <v>0.1</v>
+        <v>0.61</v>
       </c>
       <c r="W232">
-        <v>0.06</v>
+        <v>0.39</v>
       </c>
       <c r="X232">
         <v>0</v>
@@ -22530,10 +22530,10 @@
         <v>0</v>
       </c>
       <c r="G233">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H233">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="I233">
         <v>0</v>
@@ -22625,10 +22625,10 @@
         <v>0</v>
       </c>
       <c r="G234">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H234">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="I234">
         <v>0</v>
@@ -22670,10 +22670,10 @@
         <v>0</v>
       </c>
       <c r="V234">
-        <v>0.11</v>
+        <v>0.57</v>
       </c>
       <c r="W234">
-        <v>0.09</v>
+        <v>0.43</v>
       </c>
       <c r="X234">
         <v>0</v>
@@ -22815,10 +22815,10 @@
         <v>0</v>
       </c>
       <c r="G236">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="H236">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="I236">
         <v>0</v>
@@ -23100,10 +23100,10 @@
         <v>0</v>
       </c>
       <c r="G239">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="H239">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="I239">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="G240">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H240">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="I240">
         <v>0</v>
@@ -23240,10 +23240,10 @@
         <v>0</v>
       </c>
       <c r="V240">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="W240">
-        <v>0.13</v>
+        <v>0.58</v>
       </c>
       <c r="X240">
         <v>0</v>
@@ -23385,10 +23385,10 @@
         <v>0</v>
       </c>
       <c r="G242">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="H242">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="I242">
         <v>0</v>
@@ -23430,10 +23430,10 @@
         <v>0</v>
       </c>
       <c r="V242">
-        <v>0.16</v>
+        <v>0.54</v>
       </c>
       <c r="W242">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="X242">
         <v>0</v>
@@ -23525,10 +23525,10 @@
         <v>0</v>
       </c>
       <c r="V243">
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
       <c r="W243">
-        <v>0.08</v>
+        <v>0.63</v>
       </c>
       <c r="X243">
         <v>0</v>
@@ -23575,10 +23575,10 @@
         <v>0</v>
       </c>
       <c r="G244">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="H244">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="I244">
         <v>0</v>
@@ -23620,10 +23620,10 @@
         <v>0</v>
       </c>
       <c r="V244">
-        <v>0.08</v>
+        <v>0.49</v>
       </c>
       <c r="W244">
-        <v>0.08</v>
+        <v>0.51</v>
       </c>
       <c r="X244">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="G245">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="H245">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="I245">
         <v>0</v>
@@ -23715,10 +23715,10 @@
         <v>0</v>
       </c>
       <c r="V245">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
       <c r="W245">
-        <v>0.09</v>
+        <v>0.55</v>
       </c>
       <c r="X245">
         <v>0</v>
@@ -23765,10 +23765,10 @@
         <v>0</v>
       </c>
       <c r="G246">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="H246">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="I246">
         <v>0</v>
@@ -23810,10 +23810,10 @@
         <v>0</v>
       </c>
       <c r="V246">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="W246">
-        <v>0.14</v>
+        <v>0.71</v>
       </c>
       <c r="X246">
         <v>0</v>
@@ -23860,10 +23860,10 @@
         <v>0</v>
       </c>
       <c r="G247">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="H247">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
       <c r="I247">
         <v>0</v>
@@ -23905,10 +23905,10 @@
         <v>0</v>
       </c>
       <c r="V247">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="W247">
-        <v>0.16</v>
+        <v>0.58</v>
       </c>
       <c r="X247">
         <v>0</v>
@@ -23955,10 +23955,10 @@
         <v>0</v>
       </c>
       <c r="G248">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H248">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="I248">
         <v>0</v>
@@ -24000,10 +24000,10 @@
         <v>0</v>
       </c>
       <c r="V248">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="W248">
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
       <c r="X248">
         <v>0</v>
@@ -24050,10 +24050,10 @@
         <v>0</v>
       </c>
       <c r="G249">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H249">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="I249">
         <v>0</v>
@@ -24095,10 +24095,10 @@
         <v>0</v>
       </c>
       <c r="V249">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="W249">
-        <v>0.23</v>
+        <v>0.77</v>
       </c>
       <c r="X249">
         <v>0</v>
@@ -24145,10 +24145,10 @@
         <v>0</v>
       </c>
       <c r="G250">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H250">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="I250">
         <v>0</v>
@@ -24240,10 +24240,10 @@
         <v>0</v>
       </c>
       <c r="G251">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H251">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="I251">
         <v>0</v>
@@ -24335,10 +24335,10 @@
         <v>0</v>
       </c>
       <c r="G252">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="H252">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="I252">
         <v>0</v>
@@ -24380,10 +24380,10 @@
         <v>0</v>
       </c>
       <c r="V252">
-        <v>0.12</v>
+        <v>0.59</v>
       </c>
       <c r="W252">
-        <v>0.08</v>
+        <v>0.41</v>
       </c>
       <c r="X252">
         <v>0</v>
@@ -24430,10 +24430,10 @@
         <v>0</v>
       </c>
       <c r="G253">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H253">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="I253">
         <v>0</v>
@@ -24525,10 +24525,10 @@
         <v>0</v>
       </c>
       <c r="G254">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H254">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="I254">
         <v>0</v>
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="V254">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="W254">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="X254">
         <v>0</v>
@@ -24620,10 +24620,10 @@
         <v>0</v>
       </c>
       <c r="G255">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="H255">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -24665,10 +24665,10 @@
         <v>0</v>
       </c>
       <c r="V255">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="W255">
-        <v>0.14</v>
+        <v>0.6</v>
       </c>
       <c r="X255">
         <v>0</v>
@@ -24715,10 +24715,10 @@
         <v>0</v>
       </c>
       <c r="G256">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H256">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="I256">
         <v>0</v>
@@ -24760,10 +24760,10 @@
         <v>0</v>
       </c>
       <c r="V256">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="W256">
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="X256">
         <v>0</v>
@@ -24855,10 +24855,10 @@
         <v>0</v>
       </c>
       <c r="V257">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="W257">
-        <v>0.14</v>
+        <v>0.9</v>
       </c>
       <c r="X257">
         <v>0</v>
@@ -24905,10 +24905,10 @@
         <v>0</v>
       </c>
       <c r="G258">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H258">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I258">
         <v>0</v>
@@ -24950,10 +24950,10 @@
         <v>0</v>
       </c>
       <c r="V258">
-        <v>0.17</v>
+        <v>0.64</v>
       </c>
       <c r="W258">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="X258">
         <v>0</v>
@@ -25000,10 +25000,10 @@
         <v>0</v>
       </c>
       <c r="G259">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="H259">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="I259">
         <v>0</v>
@@ -25045,10 +25045,10 @@
         <v>0</v>
       </c>
       <c r="V259">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="W259">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="X259">
         <v>0</v>
@@ -25095,10 +25095,10 @@
         <v>0</v>
       </c>
       <c r="G260">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="H260">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -25140,10 +25140,10 @@
         <v>0</v>
       </c>
       <c r="V260">
-        <v>0.09</v>
+        <v>0.42</v>
       </c>
       <c r="W260">
-        <v>0.13</v>
+        <v>0.58</v>
       </c>
       <c r="X260">
         <v>0</v>
@@ -25190,10 +25190,10 @@
         <v>0</v>
       </c>
       <c r="G261">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H261">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -25235,10 +25235,10 @@
         <v>0</v>
       </c>
       <c r="V261">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="W261">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
       <c r="X261">
         <v>0</v>
@@ -25285,10 +25285,10 @@
         <v>0</v>
       </c>
       <c r="G262">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="H262">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -25330,10 +25330,10 @@
         <v>0</v>
       </c>
       <c r="V262">
-        <v>0.1</v>
+        <v>0.53</v>
       </c>
       <c r="W262">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="X262">
         <v>0</v>
@@ -25380,10 +25380,10 @@
         <v>0</v>
       </c>
       <c r="G263">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="H263">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -25475,10 +25475,10 @@
         <v>0</v>
       </c>
       <c r="G264">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H264">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -25520,10 +25520,10 @@
         <v>0</v>
       </c>
       <c r="V264">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="W264">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="X264">
         <v>0</v>
@@ -25570,10 +25570,10 @@
         <v>0</v>
       </c>
       <c r="G265">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H265">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="I265">
         <v>0</v>
@@ -25615,10 +25615,10 @@
         <v>0</v>
       </c>
       <c r="V265">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="W265">
-        <v>0.14</v>
+        <v>0.64</v>
       </c>
       <c r="X265">
         <v>0</v>
@@ -25710,10 +25710,10 @@
         <v>0</v>
       </c>
       <c r="V266">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="W266">
-        <v>0.27</v>
+        <v>0.95</v>
       </c>
       <c r="X266">
         <v>0</v>
@@ -25760,10 +25760,10 @@
         <v>0</v>
       </c>
       <c r="G267">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H267">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="I267">
         <v>0</v>
@@ -25805,10 +25805,10 @@
         <v>0</v>
       </c>
       <c r="V267">
-        <v>0.06</v>
+        <v>0.27</v>
       </c>
       <c r="W267">
-        <v>0.16</v>
+        <v>0.73</v>
       </c>
       <c r="X267">
         <v>0</v>
@@ -25855,10 +25855,10 @@
         <v>0</v>
       </c>
       <c r="G268">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H268">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="I268">
         <v>0</v>
@@ -25900,10 +25900,10 @@
         <v>0</v>
       </c>
       <c r="V268">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="W268">
-        <v>0.14</v>
+        <v>0.83</v>
       </c>
       <c r="X268">
         <v>0</v>
@@ -25950,10 +25950,10 @@
         <v>0</v>
       </c>
       <c r="G269">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H269">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="I269">
         <v>0</v>
@@ -25995,10 +25995,10 @@
         <v>0</v>
       </c>
       <c r="V269">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="W269">
-        <v>0.15</v>
+        <v>0.76</v>
       </c>
       <c r="X269">
         <v>0</v>
@@ -26140,10 +26140,10 @@
         <v>0</v>
       </c>
       <c r="G271">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="H271">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I271">
         <v>0</v>
@@ -26185,10 +26185,10 @@
         <v>0</v>
       </c>
       <c r="V271">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="W271">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="X271">
         <v>0</v>
@@ -26235,10 +26235,10 @@
         <v>0</v>
       </c>
       <c r="G272">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H272">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="I272">
         <v>0</v>
@@ -26330,10 +26330,10 @@
         <v>0</v>
       </c>
       <c r="G273">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H273">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="I273">
         <v>0</v>
@@ -26375,10 +26375,10 @@
         <v>0</v>
       </c>
       <c r="V273">
-        <v>0.07000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="W273">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="X273">
         <v>0</v>
@@ -26425,10 +26425,10 @@
         <v>0</v>
       </c>
       <c r="G274">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H274">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="I274">
         <v>0</v>
@@ -26470,10 +26470,10 @@
         <v>0</v>
       </c>
       <c r="V274">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="W274">
-        <v>0.14</v>
+        <v>0.6</v>
       </c>
       <c r="X274">
         <v>0</v>
@@ -26520,10 +26520,10 @@
         <v>0</v>
       </c>
       <c r="G275">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H275">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="I275">
         <v>0</v>
@@ -26565,10 +26565,10 @@
         <v>0</v>
       </c>
       <c r="V275">
-        <v>0.11</v>
+        <v>0.41</v>
       </c>
       <c r="W275">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="X275">
         <v>0</v>
@@ -26615,10 +26615,10 @@
         <v>0</v>
       </c>
       <c r="G276">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="H276">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="I276">
         <v>0</v>
@@ -26660,10 +26660,10 @@
         <v>0</v>
       </c>
       <c r="V276">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="W276">
-        <v>0.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="X276">
         <v>0</v>
@@ -26710,10 +26710,10 @@
         <v>0</v>
       </c>
       <c r="G277">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H277">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="I277">
         <v>0</v>
@@ -26755,10 +26755,10 @@
         <v>0</v>
       </c>
       <c r="V277">
-        <v>0.11</v>
+        <v>0.65</v>
       </c>
       <c r="W277">
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="X277">
         <v>0</v>
@@ -26805,10 +26805,10 @@
         <v>0</v>
       </c>
       <c r="G278">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="H278">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="I278">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="V278">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="W278">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
       <c r="X278">
         <v>0</v>
@@ -26945,10 +26945,10 @@
         <v>0</v>
       </c>
       <c r="V279">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="W279">
-        <v>0.15</v>
+        <v>0.67</v>
       </c>
       <c r="X279">
         <v>0</v>
@@ -26995,10 +26995,10 @@
         <v>0</v>
       </c>
       <c r="G280">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="H280">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="I280">
         <v>0</v>
@@ -27040,10 +27040,10 @@
         <v>0</v>
       </c>
       <c r="V280">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="W280">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="X280">
         <v>0</v>
@@ -27090,10 +27090,10 @@
         <v>0</v>
       </c>
       <c r="G281">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H281">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="I281">
         <v>0</v>
@@ -27185,10 +27185,10 @@
         <v>0</v>
       </c>
       <c r="G282">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H282">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="I282">
         <v>0</v>
@@ -27230,10 +27230,10 @@
         <v>0</v>
       </c>
       <c r="V282">
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
       <c r="W282">
-        <v>0.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X282">
         <v>0</v>
@@ -27280,10 +27280,10 @@
         <v>0</v>
       </c>
       <c r="G283">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H283">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="I283">
         <v>0</v>
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="V283">
-        <v>0.09</v>
+        <v>0.4</v>
       </c>
       <c r="W283">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="X283">
         <v>0</v>
@@ -27375,10 +27375,10 @@
         <v>0</v>
       </c>
       <c r="G284">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H284">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="I284">
         <v>0</v>
@@ -27420,10 +27420,10 @@
         <v>0</v>
       </c>
       <c r="V284">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="W284">
-        <v>0.12</v>
+        <v>0.61</v>
       </c>
       <c r="X284">
         <v>0</v>
@@ -27515,10 +27515,10 @@
         <v>0</v>
       </c>
       <c r="V285">
-        <v>0.1</v>
+        <v>0.66</v>
       </c>
       <c r="W285">
-        <v>0.05</v>
+        <v>0.34</v>
       </c>
       <c r="X285">
         <v>0</v>
@@ -27565,10 +27565,10 @@
         <v>0</v>
       </c>
       <c r="G286">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H286">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="I286">
         <v>0</v>
@@ -27610,10 +27610,10 @@
         <v>0</v>
       </c>
       <c r="V286">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="W286">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="X286">
         <v>0</v>
@@ -27660,10 +27660,10 @@
         <v>0</v>
       </c>
       <c r="G287">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="H287">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="I287">
         <v>0</v>
@@ -27705,10 +27705,10 @@
         <v>0</v>
       </c>
       <c r="V287">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="W287">
-        <v>0.13</v>
+        <v>0.62</v>
       </c>
       <c r="X287">
         <v>0</v>
@@ -27755,10 +27755,10 @@
         <v>0</v>
       </c>
       <c r="G288">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="H288">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="I288">
         <v>0</v>
@@ -27800,10 +27800,10 @@
         <v>0</v>
       </c>
       <c r="V288">
-        <v>0.12</v>
+        <v>0.62</v>
       </c>
       <c r="W288">
-        <v>0.07000000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="X288">
         <v>0</v>
@@ -27850,10 +27850,10 @@
         <v>0</v>
       </c>
       <c r="G289">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H289">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="I289">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="V289">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="W289">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="X289">
         <v>0</v>
@@ -27945,10 +27945,10 @@
         <v>0</v>
       </c>
       <c r="G290">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H290">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="I290">
         <v>0</v>
@@ -27990,10 +27990,10 @@
         <v>0</v>
       </c>
       <c r="V290">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="W290">
-        <v>0.11</v>
+        <v>0.53</v>
       </c>
       <c r="X290">
         <v>0</v>
@@ -28040,10 +28040,10 @@
         <v>0</v>
       </c>
       <c r="G291">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="H291">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="I291">
         <v>0</v>
@@ -28135,10 +28135,10 @@
         <v>0</v>
       </c>
       <c r="G292">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="H292">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="I292">
         <v>0</v>
@@ -28180,10 +28180,10 @@
         <v>0</v>
       </c>
       <c r="V292">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="W292">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="X292">
         <v>0</v>
@@ -28230,10 +28230,10 @@
         <v>0</v>
       </c>
       <c r="G293">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H293">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="I293">
         <v>0</v>
@@ -28275,10 +28275,10 @@
         <v>0</v>
       </c>
       <c r="V293">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="W293">
-        <v>0.19</v>
+        <v>0.82</v>
       </c>
       <c r="X293">
         <v>0</v>
@@ -28325,10 +28325,10 @@
         <v>0</v>
       </c>
       <c r="G294">
-        <v>0.52</v>
+        <v>0.79</v>
       </c>
       <c r="H294">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="I294">
         <v>0</v>
@@ -28370,10 +28370,10 @@
         <v>0</v>
       </c>
       <c r="V294">
-        <v>0.25</v>
+        <v>0.97</v>
       </c>
       <c r="W294">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="X294">
         <v>0</v>
@@ -28420,7 +28420,7 @@
         <v>0</v>
       </c>
       <c r="G295">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H295">
         <v>0</v>
@@ -28465,7 +28465,7 @@
         <v>0</v>
       </c>
       <c r="V295">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="W295">
         <v>0</v>
@@ -28515,10 +28515,10 @@
         <v>0</v>
       </c>
       <c r="G296">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="H296">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I296">
         <v>0</v>
@@ -28560,7 +28560,7 @@
         <v>0</v>
       </c>
       <c r="V296">
-        <v>0.41</v>
+        <v>1</v>
       </c>
       <c r="W296">
         <v>0</v>
@@ -28610,10 +28610,10 @@
         <v>0</v>
       </c>
       <c r="G297">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H297">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I297">
         <v>0</v>
@@ -28655,7 +28655,7 @@
         <v>0</v>
       </c>
       <c r="V297">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="W297">
         <v>0</v>
@@ -28705,10 +28705,10 @@
         <v>0</v>
       </c>
       <c r="G298">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="H298">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I298">
         <v>0</v>
@@ -28750,7 +28750,7 @@
         <v>0</v>
       </c>
       <c r="V298">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="W298">
         <v>0</v>
@@ -28800,7 +28800,7 @@
         <v>0</v>
       </c>
       <c r="G299">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="H299">
         <v>0</v>
@@ -28845,7 +28845,7 @@
         <v>0</v>
       </c>
       <c r="V299">
-        <v>0.29</v>
+        <v>1</v>
       </c>
       <c r="W299">
         <v>0</v>
@@ -28895,10 +28895,10 @@
         <v>0</v>
       </c>
       <c r="G300">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H300">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I300">
         <v>0</v>
@@ -28940,7 +28940,7 @@
         <v>0</v>
       </c>
       <c r="V300">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="W300">
         <v>0</v>
@@ -28990,7 +28990,7 @@
         <v>0</v>
       </c>
       <c r="G301">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -29035,7 +29035,7 @@
         <v>0</v>
       </c>
       <c r="V301">
-        <v>0.22</v>
+        <v>1</v>
       </c>
       <c r="W301">
         <v>0</v>
@@ -29085,10 +29085,10 @@
         <v>0</v>
       </c>
       <c r="G302">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="H302">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="I302">
         <v>0</v>
@@ -29130,7 +29130,7 @@
         <v>0</v>
       </c>
       <c r="V302">
-        <v>0.34</v>
+        <v>1</v>
       </c>
       <c r="W302">
         <v>0</v>
@@ -29180,7 +29180,7 @@
         <v>0</v>
       </c>
       <c r="G303">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="H303">
         <v>0.03</v>
@@ -29275,10 +29275,10 @@
         <v>0</v>
       </c>
       <c r="G304">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="H304">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="I304">
         <v>0</v>
@@ -29320,10 +29320,10 @@
         <v>0</v>
       </c>
       <c r="V304">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="W304">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="X304">
         <v>0</v>
@@ -29370,7 +29370,7 @@
         <v>0</v>
       </c>
       <c r="G305">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="H305">
         <v>0</v>
@@ -29415,10 +29415,10 @@
         <v>0</v>
       </c>
       <c r="V305">
-        <v>0.24</v>
+        <v>0.99</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="X305">
         <v>0</v>

--- a/outline_prediction_comparison.xlsx
+++ b/outline_prediction_comparison.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/amit/BIO/FINAL/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0366BDF2-57ED-5F46-9955-AF2765B1A84C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="500" yWindow="2460" windowWidth="29340" windowHeight="13700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -118,8 +124,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,13 +188,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -226,7 +240,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -260,6 +274,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -294,9 +309,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,11 +485,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE305"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" customWidth="1"/>
+    <col min="19" max="19" width="19.1640625" customWidth="1"/>
+    <col min="20" max="20" width="14.5" customWidth="1"/>
+    <col min="21" max="21" width="21.5" customWidth="1"/>
+    <col min="22" max="22" width="22.33203125" customWidth="1"/>
+    <col min="23" max="23" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +595,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -576,7 +606,7 @@
         <v>5.35</v>
       </c>
       <c r="D2">
-        <v>75.18000000000001</v>
+        <v>75.180000000000007</v>
       </c>
       <c r="E2">
         <v>107.62</v>
@@ -621,7 +651,7 @@
         <v>5.67</v>
       </c>
       <c r="S2">
-        <v>70.04000000000001</v>
+        <v>70.040000000000006</v>
       </c>
       <c r="T2">
         <v>59.39</v>
@@ -660,7 +690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -674,7 +704,7 @@
         <v>75.61</v>
       </c>
       <c r="E3">
-        <v>84.48999999999999</v>
+        <v>84.49</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -740,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>581.9400000000001</v>
+        <v>581.94000000000005</v>
       </c>
       <c r="AB3">
         <v>609.66</v>
@@ -755,7 +785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -766,7 +796,7 @@
         <v>6.31</v>
       </c>
       <c r="D4">
-        <v>68.01000000000001</v>
+        <v>68.010000000000005</v>
       </c>
       <c r="E4">
         <v>94.73</v>
@@ -778,7 +808,7 @@
         <v>0.93</v>
       </c>
       <c r="H4">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -793,7 +823,7 @@
         <v>671.61</v>
       </c>
       <c r="M4">
-        <v>282.71</v>
+        <v>282.70999999999998</v>
       </c>
       <c r="N4" t="s">
         <v>30</v>
@@ -850,7 +880,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -945,7 +975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -959,7 +989,7 @@
         <v>57.42</v>
       </c>
       <c r="E6">
-        <v>90.43000000000001</v>
+        <v>90.43</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -998,7 +1028,7 @@
         <v>24632</v>
       </c>
       <c r="R6">
-        <v>9.539999999999999</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="S6">
         <v>48.12</v>
@@ -1040,7 +1070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1048,13 +1078,13 @@
         <v>61763</v>
       </c>
       <c r="C7">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="D7">
         <v>40.22</v>
       </c>
       <c r="E7">
-        <v>66.15000000000001</v>
+        <v>66.150000000000006</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1135,7 +1165,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1173,7 +1203,7 @@
         <v>246.38</v>
       </c>
       <c r="M8">
-        <v>581.45</v>
+        <v>581.45000000000005</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -1230,7 +1260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1313,7 +1343,7 @@
         <v>538.78</v>
       </c>
       <c r="AB9">
-        <v>753.3099999999999</v>
+        <v>753.31</v>
       </c>
       <c r="AC9" t="s">
         <v>30</v>
@@ -1325,7 +1355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1384,7 +1414,7 @@
         <v>87.25</v>
       </c>
       <c r="T10">
-        <v>65.15000000000001</v>
+        <v>65.150000000000006</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1420,7 +1450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1458,7 +1488,7 @@
         <v>549.46</v>
       </c>
       <c r="M11">
-        <v>570.08</v>
+        <v>570.08000000000004</v>
       </c>
       <c r="N11" t="s">
         <v>30</v>
@@ -1479,7 +1509,7 @@
         <v>59.46</v>
       </c>
       <c r="T11">
-        <v>34.98</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -1515,7 +1545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1550,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>789.4299999999999</v>
+        <v>789.43</v>
       </c>
       <c r="M12">
-        <v>595.5599999999999</v>
+        <v>595.55999999999995</v>
       </c>
       <c r="N12" t="s">
         <v>30</v>
@@ -1598,7 +1628,7 @@
         <v>810.83</v>
       </c>
       <c r="AB12">
-        <v>554.8200000000001</v>
+        <v>554.82000000000005</v>
       </c>
       <c r="AC12" t="s">
         <v>30</v>
@@ -1610,7 +1640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1618,7 +1648,7 @@
         <v>81070</v>
       </c>
       <c r="C13">
-        <v>4.69</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="D13">
         <v>36.21</v>
@@ -1630,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H13">
         <v>0.19</v>
@@ -1645,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1064.09</v>
+        <v>1064.0899999999999</v>
       </c>
       <c r="M13">
         <v>381.87</v>
@@ -1663,10 +1693,10 @@
         <v>61351</v>
       </c>
       <c r="R13">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="S13">
-        <v>35.13</v>
+        <v>35.130000000000003</v>
       </c>
       <c r="T13">
         <v>31</v>
@@ -1705,7 +1735,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1725,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H14">
         <v>0.19</v>
@@ -1800,7 +1830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1895,7 +1925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1948,7 +1978,7 @@
         <v>7373</v>
       </c>
       <c r="R16">
-        <v>5.11</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="S16">
         <v>122.51</v>
@@ -1990,7 +2020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2001,7 +2031,7 @@
         <v>6.51</v>
       </c>
       <c r="D17">
-        <v>79.81999999999999</v>
+        <v>79.819999999999993</v>
       </c>
       <c r="E17">
         <v>144.57</v>
@@ -2025,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>904.6900000000001</v>
+        <v>904.69</v>
       </c>
       <c r="M17">
         <v>453.38</v>
@@ -2085,7 +2115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2123,7 +2153,7 @@
         <v>555.14</v>
       </c>
       <c r="M18">
-        <v>725.9400000000001</v>
+        <v>725.94</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -2165,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>557.7</v>
+        <v>557.70000000000005</v>
       </c>
       <c r="AB18">
         <v>733.12</v>
@@ -2180,7 +2210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2194,7 +2224,7 @@
         <v>110.03</v>
       </c>
       <c r="E19">
-        <v>98.34999999999999</v>
+        <v>98.35</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2215,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>663.4299999999999</v>
+        <v>663.43</v>
       </c>
       <c r="M19">
         <v>484</v>
@@ -2260,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>597.95</v>
+        <v>597.95000000000005</v>
       </c>
       <c r="AB19">
         <v>384.34</v>
@@ -2275,7 +2305,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:31">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2370,7 +2400,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2384,7 +2414,7 @@
         <v>79.53</v>
       </c>
       <c r="E21">
-        <v>94.09999999999999</v>
+        <v>94.1</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2423,7 +2453,7 @@
         <v>44723</v>
       </c>
       <c r="R21">
-        <v>8.199999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="S21">
         <v>77.73</v>
@@ -2465,7 +2495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2560,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2655,7 +2685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2750,7 +2780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2761,7 +2791,7 @@
         <v>6.54</v>
       </c>
       <c r="D25">
-        <v>99.54000000000001</v>
+        <v>99.54</v>
       </c>
       <c r="E25">
         <v>106.79</v>
@@ -2806,7 +2836,7 @@
         <v>8.91</v>
       </c>
       <c r="S25">
-        <v>82.59999999999999</v>
+        <v>82.6</v>
       </c>
       <c r="T25">
         <v>66.14</v>
@@ -2845,7 +2875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2898,10 +2928,10 @@
         <v>34954</v>
       </c>
       <c r="R26">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="S26">
-        <v>90.68000000000001</v>
+        <v>90.68</v>
       </c>
       <c r="T26">
         <v>44.48</v>
@@ -2940,7 +2970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2951,7 +2981,7 @@
         <v>6.42</v>
       </c>
       <c r="D27">
-        <v>79.09999999999999</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="E27">
         <v>62.01</v>
@@ -2975,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>1137.87</v>
+        <v>1137.8699999999999</v>
       </c>
       <c r="M27">
         <v>368.26</v>
@@ -3020,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>1116.14</v>
+        <v>1116.1400000000001</v>
       </c>
       <c r="AB27">
         <v>389.89</v>
@@ -3035,7 +3065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3055,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H28">
         <v>0.06</v>
@@ -3130,7 +3160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:31">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3144,7 +3174,7 @@
         <v>54.81</v>
       </c>
       <c r="E29">
-        <v>136.23</v>
+        <v>136.22999999999999</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -3183,7 +3213,7 @@
         <v>24195</v>
       </c>
       <c r="R29">
-        <v>4.94</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="S29">
         <v>47.75</v>
@@ -3213,7 +3243,7 @@
         <v>290.33</v>
       </c>
       <c r="AB29">
-        <v>715.1799999999999</v>
+        <v>715.18</v>
       </c>
       <c r="AC29" t="s">
         <v>30</v>
@@ -3225,7 +3255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3320,7 +3350,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3355,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>303.16</v>
+        <v>303.16000000000003</v>
       </c>
       <c r="M31">
         <v>466.68</v>
@@ -3373,13 +3403,13 @@
         <v>15391</v>
       </c>
       <c r="R31">
-        <v>4.89</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="S31">
         <v>37.28</v>
       </c>
       <c r="T31">
-        <v>73.65000000000001</v>
+        <v>73.650000000000006</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -3415,7 +3445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3426,7 +3456,7 @@
         <v>6.84</v>
       </c>
       <c r="D32">
-        <v>92.59999999999999</v>
+        <v>92.6</v>
       </c>
       <c r="E32">
         <v>135.85</v>
@@ -3471,7 +3501,7 @@
         <v>7.44</v>
       </c>
       <c r="S32">
-        <v>85.81999999999999</v>
+        <v>85.82</v>
       </c>
       <c r="T32">
         <v>69.59</v>
@@ -3510,7 +3540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3548,7 +3578,7 @@
         <v>512.61</v>
       </c>
       <c r="M33">
-        <v>749.1799999999999</v>
+        <v>749.18</v>
       </c>
       <c r="N33" t="s">
         <v>30</v>
@@ -3566,7 +3596,7 @@
         <v>8.06</v>
       </c>
       <c r="S33">
-        <v>65.73999999999999</v>
+        <v>65.739999999999995</v>
       </c>
       <c r="T33">
         <v>64.27</v>
@@ -3605,7 +3635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3640,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>647.7</v>
+        <v>647.70000000000005</v>
       </c>
       <c r="M34">
         <v>463.64</v>
@@ -3700,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3738,7 +3768,7 @@
         <v>777.39</v>
       </c>
       <c r="M35">
-        <v>786.3200000000001</v>
+        <v>786.32</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -3795,7 +3825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3830,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>748.1799999999999</v>
+        <v>748.18</v>
       </c>
       <c r="M36">
         <v>323.77</v>
@@ -3854,7 +3884,7 @@
         <v>76.97</v>
       </c>
       <c r="T36">
-        <v>70.93000000000001</v>
+        <v>70.930000000000007</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -3890,7 +3920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3985,7 +4015,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3996,7 +4026,7 @@
         <v>5.73</v>
       </c>
       <c r="D38">
-        <v>67.09999999999999</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="E38">
         <v>92.83</v>
@@ -4020,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1025.84</v>
+        <v>1025.8399999999999</v>
       </c>
       <c r="M38">
         <v>584.37</v>
@@ -4038,7 +4068,7 @@
         <v>51552</v>
       </c>
       <c r="R38">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="S38">
         <v>61.48</v>
@@ -4065,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1152.35</v>
+        <v>1152.3499999999999</v>
       </c>
       <c r="AB38">
         <v>566.38</v>
@@ -4080,7 +4110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4175,7 +4205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4270,7 +4300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4353,7 +4383,7 @@
         <v>628.01</v>
       </c>
       <c r="AB41">
-        <v>327.47</v>
+        <v>327.47000000000003</v>
       </c>
       <c r="AC41" t="s">
         <v>30</v>
@@ -4365,7 +4395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4460,7 +4490,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4516,10 +4546,10 @@
         <v>5.31</v>
       </c>
       <c r="S43">
-        <v>36.13</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="T43">
-        <v>70.40000000000001</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -4555,7 +4585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:31">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4593,7 +4623,7 @@
         <v>828.01</v>
       </c>
       <c r="M44">
-        <v>555.05</v>
+        <v>555.04999999999995</v>
       </c>
       <c r="N44" t="s">
         <v>30</v>
@@ -4638,7 +4668,7 @@
         <v>830.64</v>
       </c>
       <c r="AB44">
-        <v>550.58</v>
+        <v>550.58000000000004</v>
       </c>
       <c r="AC44" t="s">
         <v>30</v>
@@ -4650,7 +4680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4706,7 +4736,7 @@
         <v>5.74</v>
       </c>
       <c r="S45">
-        <v>65.06999999999999</v>
+        <v>65.069999999999993</v>
       </c>
       <c r="T45">
         <v>53.61</v>
@@ -4745,7 +4775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4783,7 +4813,7 @@
         <v>1072.56</v>
       </c>
       <c r="M46">
-        <v>587.58</v>
+        <v>587.58000000000004</v>
       </c>
       <c r="N46" t="s">
         <v>30</v>
@@ -4825,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>1074.11</v>
+        <v>1074.1099999999999</v>
       </c>
       <c r="AB46">
         <v>586.63</v>
@@ -4840,7 +4870,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4851,10 +4881,10 @@
         <v>4.79</v>
       </c>
       <c r="D47">
-        <v>89.18000000000001</v>
+        <v>89.18</v>
       </c>
       <c r="E47">
-        <v>84.93000000000001</v>
+        <v>84.93</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -4875,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1265.85</v>
+        <v>1265.8499999999999</v>
       </c>
       <c r="M47">
         <v>505.8</v>
@@ -4920,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1266.13</v>
+        <v>1266.1300000000001</v>
       </c>
       <c r="AB47">
         <v>505.5</v>
@@ -4935,7 +4965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4958,7 +4988,7 @@
         <v>0.93</v>
       </c>
       <c r="H48">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5030,7 +5060,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:31">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5041,7 +5071,7 @@
         <v>3.74</v>
       </c>
       <c r="D49">
-        <v>84.81999999999999</v>
+        <v>84.82</v>
       </c>
       <c r="E49">
         <v>58.01</v>
@@ -5050,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H49">
         <v>0.19</v>
@@ -5086,7 +5116,7 @@
         <v>4.79</v>
       </c>
       <c r="S49">
-        <v>90.90000000000001</v>
+        <v>90.9</v>
       </c>
       <c r="T49">
         <v>13.78</v>
@@ -5095,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="V49">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W49">
         <v>0.06</v>
@@ -5125,7 +5155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5220,7 +5250,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -5240,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H51">
         <v>0.06</v>
@@ -5303,7 +5333,7 @@
         <v>439.56</v>
       </c>
       <c r="AB51">
-        <v>560.42</v>
+        <v>560.41999999999996</v>
       </c>
       <c r="AC51" t="s">
         <v>30</v>
@@ -5315,7 +5345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -5326,7 +5356,7 @@
         <v>6.63</v>
       </c>
       <c r="D52">
-        <v>67.59999999999999</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="E52">
         <v>124.43</v>
@@ -5350,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>644.42</v>
+        <v>644.41999999999996</v>
       </c>
       <c r="M52">
         <v>849.22</v>
@@ -5410,7 +5440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="1:31">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -5421,7 +5451,7 @@
         <v>7.52</v>
       </c>
       <c r="D53">
-        <v>40.23</v>
+        <v>40.229999999999997</v>
       </c>
       <c r="E53">
         <v>114.06</v>
@@ -5505,7 +5535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -5600,7 +5630,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -5614,7 +5644,7 @@
         <v>90.36</v>
       </c>
       <c r="E55">
-        <v>136.23</v>
+        <v>136.22999999999999</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -5695,7 +5725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:31">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -5706,7 +5736,7 @@
         <v>5.99</v>
       </c>
       <c r="D56">
-        <v>89.43000000000001</v>
+        <v>89.43</v>
       </c>
       <c r="E56">
         <v>118.55</v>
@@ -5790,7 +5820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:31">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -5828,7 +5858,7 @@
         <v>774.02</v>
       </c>
       <c r="M57">
-        <v>619.58</v>
+        <v>619.58000000000004</v>
       </c>
       <c r="N57" t="s">
         <v>30</v>
@@ -5885,7 +5915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:31">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -5980,7 +6010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:31">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6018,7 +6048,7 @@
         <v>1172.04</v>
       </c>
       <c r="M59">
-        <v>533.67</v>
+        <v>533.66999999999996</v>
       </c>
       <c r="N59" t="s">
         <v>30</v>
@@ -6036,7 +6066,7 @@
         <v>1.79</v>
       </c>
       <c r="S59">
-        <v>96.23999999999999</v>
+        <v>96.24</v>
       </c>
       <c r="T59">
         <v>51.41</v>
@@ -6060,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1106.64</v>
+        <v>1106.6400000000001</v>
       </c>
       <c r="AB59">
         <v>539.91</v>
@@ -6075,7 +6105,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:31">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6086,7 +6116,7 @@
         <v>2.91</v>
       </c>
       <c r="D60">
-        <v>73.09999999999999</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="E60">
         <v>84.98</v>
@@ -6134,7 +6164,7 @@
         <v>79.28</v>
       </c>
       <c r="T60">
-        <v>34.87</v>
+        <v>34.869999999999997</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -6143,7 +6173,7 @@
         <v>0.31</v>
       </c>
       <c r="W60">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X60">
         <v>0</v>
@@ -6170,7 +6200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:31">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6184,7 +6214,7 @@
         <v>43.89</v>
       </c>
       <c r="E61">
-        <v>78.56999999999999</v>
+        <v>78.569999999999993</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -6205,10 +6235,10 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>262.16</v>
+        <v>262.16000000000003</v>
       </c>
       <c r="M61">
-        <v>750.9299999999999</v>
+        <v>750.93</v>
       </c>
       <c r="N61" t="s">
         <v>31</v>
@@ -6223,7 +6253,7 @@
         <v>56077</v>
       </c>
       <c r="R61">
-        <v>5.11</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="S61">
         <v>43.86</v>
@@ -6265,7 +6295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:31">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6321,7 +6351,7 @@
         <v>3.56</v>
       </c>
       <c r="S62">
-        <v>88.23999999999999</v>
+        <v>88.24</v>
       </c>
       <c r="T62">
         <v>36.26</v>
@@ -6360,7 +6390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:31">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6371,7 +6401,7 @@
         <v>2.14</v>
       </c>
       <c r="D63">
-        <v>138.45</v>
+        <v>138.44999999999999</v>
       </c>
       <c r="E63">
         <v>98.17</v>
@@ -6398,7 +6428,7 @@
         <v>501.59</v>
       </c>
       <c r="M63">
-        <v>621.33</v>
+        <v>621.33000000000004</v>
       </c>
       <c r="N63" t="s">
         <v>31</v>
@@ -6413,13 +6443,13 @@
         <v>31036</v>
       </c>
       <c r="R63">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="S63">
-        <v>147.64</v>
+        <v>147.63999999999999</v>
       </c>
       <c r="T63">
-        <v>79.48999999999999</v>
+        <v>79.489999999999995</v>
       </c>
       <c r="U63">
         <v>0</v>
@@ -6443,7 +6473,7 @@
         <v>497.51</v>
       </c>
       <c r="AB63">
-        <v>622.6900000000001</v>
+        <v>622.69000000000005</v>
       </c>
       <c r="AC63" t="s">
         <v>31</v>
@@ -6455,7 +6485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:31">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6493,7 +6523,7 @@
         <v>789.6</v>
       </c>
       <c r="M64">
-        <v>648.2</v>
+        <v>648.20000000000005</v>
       </c>
       <c r="N64" t="s">
         <v>31</v>
@@ -6523,7 +6553,7 @@
         <v>0.19</v>
       </c>
       <c r="W64">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X64">
         <v>0</v>
@@ -6550,7 +6580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6645,7 +6675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6659,7 +6689,7 @@
         <v>79.87</v>
       </c>
       <c r="E66">
-        <v>86.29000000000001</v>
+        <v>86.29</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -6701,7 +6731,7 @@
         <v>1.78</v>
       </c>
       <c r="S66">
-        <v>77.68000000000001</v>
+        <v>77.680000000000007</v>
       </c>
       <c r="T66">
         <v>59.45</v>
@@ -6740,7 +6770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="67" spans="1:31">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6835,7 +6865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6870,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>1057.65</v>
+        <v>1057.6500000000001</v>
       </c>
       <c r="M68">
         <v>535.29</v>
@@ -6930,7 +6960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6986,7 +7016,7 @@
         <v>2.21</v>
       </c>
       <c r="S69">
-        <v>69.29000000000001</v>
+        <v>69.290000000000006</v>
       </c>
       <c r="T69">
         <v>54.39</v>
@@ -7025,7 +7055,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -7033,7 +7063,7 @@
         <v>53150</v>
       </c>
       <c r="C70">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D70">
         <v>61.55</v>
@@ -7105,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1199.85</v>
+        <v>1199.8499999999999</v>
       </c>
       <c r="AB70">
         <v>777.9</v>
@@ -7120,7 +7150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:31">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7140,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H71">
         <v>0.43</v>
@@ -7200,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>141.27</v>
+        <v>141.27000000000001</v>
       </c>
       <c r="AB71">
         <v>626.25</v>
@@ -7215,7 +7245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7223,7 +7253,7 @@
         <v>40005</v>
       </c>
       <c r="C72">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="D72">
         <v>47.46</v>
@@ -7310,7 +7340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7405,7 +7435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -7419,7 +7449,7 @@
         <v>63.12</v>
       </c>
       <c r="E74">
-        <v>80.79000000000001</v>
+        <v>80.790000000000006</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -7440,10 +7470,10 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>550.45</v>
+        <v>550.45000000000005</v>
       </c>
       <c r="M74">
-        <v>709.8099999999999</v>
+        <v>709.81</v>
       </c>
       <c r="N74" t="s">
         <v>31</v>
@@ -7473,7 +7503,7 @@
         <v>0.19</v>
       </c>
       <c r="W74">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X74">
         <v>0</v>
@@ -7485,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>551.95</v>
+        <v>551.95000000000005</v>
       </c>
       <c r="AB74">
         <v>666.79</v>
@@ -7500,7 +7530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7556,7 +7586,7 @@
         <v>1.56</v>
       </c>
       <c r="S75">
-        <v>88.34999999999999</v>
+        <v>88.35</v>
       </c>
       <c r="T75">
         <v>56.54</v>
@@ -7595,7 +7625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -7609,7 +7639,7 @@
         <v>82.8</v>
       </c>
       <c r="E76">
-        <v>88.81999999999999</v>
+        <v>88.82</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -7651,7 +7681,7 @@
         <v>1.66</v>
       </c>
       <c r="S76">
-        <v>88.65000000000001</v>
+        <v>88.65</v>
       </c>
       <c r="T76">
         <v>49.04</v>
@@ -7663,7 +7693,7 @@
         <v>0.19</v>
       </c>
       <c r="W76">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X76">
         <v>0</v>
@@ -7690,7 +7720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -7704,7 +7734,7 @@
         <v>87.73</v>
       </c>
       <c r="E77">
-        <v>83.70999999999999</v>
+        <v>83.71</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -7770,7 +7800,7 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>761.9400000000001</v>
+        <v>761.94</v>
       </c>
       <c r="AB77">
         <v>304.25</v>
@@ -7785,7 +7815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7796,10 +7826,10 @@
         <v>4.8</v>
       </c>
       <c r="D78">
-        <v>67.98999999999999</v>
+        <v>67.989999999999995</v>
       </c>
       <c r="E78">
-        <v>98.23999999999999</v>
+        <v>98.24</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -7820,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>881.0599999999999</v>
+        <v>881.06</v>
       </c>
       <c r="M78">
         <v>571.35</v>
@@ -7880,7 +7910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7894,7 +7924,7 @@
         <v>61.18</v>
       </c>
       <c r="E79">
-        <v>90.43000000000001</v>
+        <v>90.43</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -7975,7 +8005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -7998,7 +8028,7 @@
         <v>0.43</v>
       </c>
       <c r="H80">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -8058,7 +8088,7 @@
         <v>345.76</v>
       </c>
       <c r="AB80">
-        <v>542.05</v>
+        <v>542.04999999999995</v>
       </c>
       <c r="AC80" t="s">
         <v>31</v>
@@ -8070,7 +8100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:31">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -8135,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="V81">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W81">
         <v>0.71</v>
@@ -8150,7 +8180,7 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>684.3099999999999</v>
+        <v>684.31</v>
       </c>
       <c r="AB81">
         <v>805.16</v>
@@ -8165,7 +8195,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -8173,10 +8203,10 @@
         <v>61419</v>
       </c>
       <c r="C82">
-        <v>4.81</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="D82">
-        <v>69.20999999999999</v>
+        <v>69.209999999999994</v>
       </c>
       <c r="E82">
         <v>86.98</v>
@@ -8221,7 +8251,7 @@
         <v>5.09</v>
       </c>
       <c r="S82">
-        <v>69.56999999999999</v>
+        <v>69.569999999999993</v>
       </c>
       <c r="T82">
         <v>56.23</v>
@@ -8260,7 +8290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:31">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -8295,7 +8325,7 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>883.9400000000001</v>
+        <v>883.94</v>
       </c>
       <c r="M83">
         <v>169.41</v>
@@ -8355,7 +8385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:31">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -8369,13 +8399,13 @@
         <v>65.81</v>
       </c>
       <c r="E84">
-        <v>78.95999999999999</v>
+        <v>78.959999999999994</v>
       </c>
       <c r="F84">
         <v>0</v>
       </c>
       <c r="G84">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H84">
         <v>0.45</v>
@@ -8390,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>1036.88</v>
+        <v>1036.8800000000001</v>
       </c>
       <c r="M84">
         <v>748.42</v>
@@ -8411,7 +8441,7 @@
         <v>3.61</v>
       </c>
       <c r="S84">
-        <v>71.79000000000001</v>
+        <v>71.790000000000006</v>
       </c>
       <c r="T84">
         <v>53.86</v>
@@ -8435,7 +8465,7 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>1100.1</v>
+        <v>1100.0999999999999</v>
       </c>
       <c r="AB84">
         <v>628.65</v>
@@ -8450,7 +8480,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:31">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -8470,7 +8500,7 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H85">
         <v>0.71</v>
@@ -8530,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>1152.16</v>
+        <v>1152.1600000000001</v>
       </c>
       <c r="AB85">
         <v>861.48</v>
@@ -8545,7 +8575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" spans="1:31">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -8640,7 +8670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:31">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -8651,7 +8681,7 @@
         <v>2.34</v>
       </c>
       <c r="D87">
-        <v>39.63</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="E87">
         <v>58.83</v>
@@ -8693,10 +8723,10 @@
         <v>57569</v>
       </c>
       <c r="R87">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="S87">
-        <v>37.45</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="T87">
         <v>24.41</v>
@@ -8735,7 +8765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:31">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -8791,7 +8821,7 @@
         <v>2.1</v>
       </c>
       <c r="S88">
-        <v>71.23999999999999</v>
+        <v>71.239999999999995</v>
       </c>
       <c r="T88">
         <v>36.69</v>
@@ -8830,7 +8860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:31">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -8868,7 +8898,7 @@
         <v>387</v>
       </c>
       <c r="M89">
-        <v>319.21</v>
+        <v>319.20999999999998</v>
       </c>
       <c r="N89" t="s">
         <v>31</v>
@@ -8925,7 +8955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:31">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -8981,7 +9011,7 @@
         <v>3.38</v>
       </c>
       <c r="S90">
-        <v>87.56999999999999</v>
+        <v>87.57</v>
       </c>
       <c r="T90">
         <v>54.95</v>
@@ -8993,7 +9023,7 @@
         <v>0.42</v>
       </c>
       <c r="W90">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X90">
         <v>0</v>
@@ -9020,7 +9050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:31">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -9115,7 +9145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:31">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -9210,7 +9240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:31">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -9224,13 +9254,13 @@
         <v>70.47</v>
       </c>
       <c r="E93">
-        <v>95.93000000000001</v>
+        <v>95.93</v>
       </c>
       <c r="F93">
         <v>0</v>
       </c>
       <c r="G93">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H93">
         <v>0.44</v>
@@ -9293,7 +9323,7 @@
         <v>952.71</v>
       </c>
       <c r="AB93">
-        <v>775.3200000000001</v>
+        <v>775.32</v>
       </c>
       <c r="AC93" t="s">
         <v>31</v>
@@ -9305,7 +9335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:31">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -9358,7 +9388,7 @@
         <v>85789</v>
       </c>
       <c r="R94">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="S94">
         <v>86.84</v>
@@ -9385,7 +9415,7 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1092.39</v>
+        <v>1092.3900000000001</v>
       </c>
       <c r="AB94">
         <v>263.37</v>
@@ -9400,7 +9430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:31">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -9414,7 +9444,7 @@
         <v>51.19</v>
       </c>
       <c r="E95">
-        <v>69.45999999999999</v>
+        <v>69.459999999999994</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -9438,7 +9468,7 @@
         <v>1187.99</v>
       </c>
       <c r="M95">
-        <v>524.83</v>
+        <v>524.83000000000004</v>
       </c>
       <c r="N95" t="s">
         <v>31</v>
@@ -9453,7 +9483,7 @@
         <v>74571</v>
       </c>
       <c r="R95">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="S95">
         <v>47.37</v>
@@ -9495,7 +9525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="96" spans="1:31">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -9503,7 +9533,7 @@
         <v>86866</v>
       </c>
       <c r="C96">
-        <v>2.43</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="D96">
         <v>52.64</v>
@@ -9563,7 +9593,7 @@
         <v>0.44</v>
       </c>
       <c r="W96">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X96">
         <v>0</v>
@@ -9590,7 +9620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:31">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -9604,7 +9634,7 @@
         <v>86.34</v>
       </c>
       <c r="E97">
-        <v>84.84999999999999</v>
+        <v>84.85</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -9646,7 +9676,7 @@
         <v>2.8</v>
       </c>
       <c r="S97">
-        <v>81.54000000000001</v>
+        <v>81.540000000000006</v>
       </c>
       <c r="T97">
         <v>114.41</v>
@@ -9685,7 +9715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:31">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -9723,7 +9753,7 @@
         <v>491.94</v>
       </c>
       <c r="M98">
-        <v>760.4400000000001</v>
+        <v>760.44</v>
       </c>
       <c r="N98" t="s">
         <v>31</v>
@@ -9744,13 +9774,13 @@
         <v>66.89</v>
       </c>
       <c r="T98">
-        <v>78.06999999999999</v>
+        <v>78.069999999999993</v>
       </c>
       <c r="U98">
         <v>0</v>
       </c>
       <c r="V98">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="W98">
         <v>0.31</v>
@@ -9780,7 +9810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:31">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -9791,7 +9821,7 @@
         <v>4.7</v>
       </c>
       <c r="D99">
-        <v>88.20999999999999</v>
+        <v>88.21</v>
       </c>
       <c r="E99">
         <v>76.63</v>
@@ -9815,10 +9845,10 @@
         <v>0</v>
       </c>
       <c r="L99">
-        <v>640.0599999999999</v>
+        <v>640.05999999999995</v>
       </c>
       <c r="M99">
-        <v>318.41</v>
+        <v>318.41000000000003</v>
       </c>
       <c r="N99" t="s">
         <v>31</v>
@@ -9836,7 +9866,7 @@
         <v>4.38</v>
       </c>
       <c r="S99">
-        <v>88.93000000000001</v>
+        <v>88.93</v>
       </c>
       <c r="T99">
         <v>48.29</v>
@@ -9875,7 +9905,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:31">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -9910,10 +9940,10 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>642.33</v>
+        <v>642.33000000000004</v>
       </c>
       <c r="M100">
-        <v>591.67</v>
+        <v>591.66999999999996</v>
       </c>
       <c r="N100" t="s">
         <v>31</v>
@@ -9958,7 +9988,7 @@
         <v>730.5</v>
       </c>
       <c r="AB100">
-        <v>572.6799999999999</v>
+        <v>572.67999999999995</v>
       </c>
       <c r="AC100" t="s">
         <v>31</v>
@@ -9970,7 +10000,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:31">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -9984,7 +10014,7 @@
         <v>66.67</v>
       </c>
       <c r="E101">
-        <v>83.09999999999999</v>
+        <v>83.1</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -10023,7 +10053,7 @@
         <v>23562</v>
       </c>
       <c r="R101">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="S101">
         <v>63.89</v>
@@ -10053,7 +10083,7 @@
         <v>866.97</v>
       </c>
       <c r="AB101">
-        <v>293.84</v>
+        <v>293.83999999999997</v>
       </c>
       <c r="AC101" t="s">
         <v>31</v>
@@ -10065,7 +10095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" spans="1:31">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -10088,7 +10118,7 @@
         <v>0.44</v>
       </c>
       <c r="H102">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -10160,7 +10190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:31">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -10198,7 +10228,7 @@
         <v>923.04</v>
       </c>
       <c r="M103">
-        <v>726.0700000000001</v>
+        <v>726.07</v>
       </c>
       <c r="N103" t="s">
         <v>31</v>
@@ -10225,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="V103">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="W103">
         <v>0.42</v>
@@ -10255,7 +10285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:31">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -10266,10 +10296,10 @@
         <v>2.81</v>
       </c>
       <c r="D104">
-        <v>39.84</v>
+        <v>39.840000000000003</v>
       </c>
       <c r="E104">
-        <v>74.65000000000001</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -10323,7 +10353,7 @@
         <v>0.71</v>
       </c>
       <c r="W104">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X104">
         <v>0</v>
@@ -10350,7 +10380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:31">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -10370,7 +10400,7 @@
         <v>0</v>
       </c>
       <c r="G105">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H105">
         <v>0.06</v>
@@ -10445,7 +10475,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:31">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -10468,7 +10498,7 @@
         <v>0.86</v>
       </c>
       <c r="H106">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -10540,7 +10570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="107" spans="1:31">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -10608,7 +10638,7 @@
         <v>0.93</v>
       </c>
       <c r="W107">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X107">
         <v>0</v>
@@ -10635,7 +10665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:31">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -10673,7 +10703,7 @@
         <v>679.33</v>
       </c>
       <c r="M108">
-        <v>322.34</v>
+        <v>322.33999999999997</v>
       </c>
       <c r="N108" t="s">
         <v>30</v>
@@ -10688,7 +10718,7 @@
         <v>25992</v>
       </c>
       <c r="R108">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="S108">
         <v>73.87</v>
@@ -10718,7 +10748,7 @@
         <v>691.36</v>
       </c>
       <c r="AB108">
-        <v>292.47</v>
+        <v>292.47000000000003</v>
       </c>
       <c r="AC108" t="s">
         <v>30</v>
@@ -10730,7 +10760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:31">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -10753,7 +10783,7 @@
         <v>0.93</v>
       </c>
       <c r="H109">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -10825,7 +10855,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:31">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -10878,10 +10908,10 @@
         <v>22877</v>
       </c>
       <c r="R110">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="S110">
-        <v>73.26000000000001</v>
+        <v>73.260000000000005</v>
       </c>
       <c r="T110">
         <v>62.99</v>
@@ -10920,7 +10950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:31">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -10934,7 +10964,7 @@
         <v>68.44</v>
       </c>
       <c r="E111">
-        <v>132.77</v>
+        <v>132.77000000000001</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -10958,7 +10988,7 @@
         <v>886.05</v>
       </c>
       <c r="M111">
-        <v>266.1</v>
+        <v>266.10000000000002</v>
       </c>
       <c r="N111" t="s">
         <v>30</v>
@@ -10979,7 +11009,7 @@
         <v>53.78</v>
       </c>
       <c r="T111">
-        <v>76.90000000000001</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="U111">
         <v>0</v>
@@ -11003,7 +11033,7 @@
         <v>886.55</v>
       </c>
       <c r="AB111">
-        <v>262.15</v>
+        <v>262.14999999999998</v>
       </c>
       <c r="AC111" t="s">
         <v>30</v>
@@ -11015,7 +11045,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:31">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -11029,7 +11059,7 @@
         <v>55.58</v>
       </c>
       <c r="E112">
-        <v>85.68000000000001</v>
+        <v>85.68</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -11038,7 +11068,7 @@
         <v>0.93</v>
       </c>
       <c r="H112">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -11053,7 +11083,7 @@
         <v>1007.09</v>
       </c>
       <c r="M112">
-        <v>686.5700000000001</v>
+        <v>686.57</v>
       </c>
       <c r="N112" t="s">
         <v>30</v>
@@ -11110,7 +11140,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:31">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -11121,7 +11151,7 @@
         <v>2.9</v>
       </c>
       <c r="D113">
-        <v>67.06999999999999</v>
+        <v>67.069999999999993</v>
       </c>
       <c r="E113">
         <v>102.62</v>
@@ -11169,7 +11199,7 @@
         <v>58.91</v>
       </c>
       <c r="T113">
-        <v>80.20999999999999</v>
+        <v>80.209999999999994</v>
       </c>
       <c r="U113">
         <v>0</v>
@@ -11205,7 +11235,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:31">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -11270,7 +11300,7 @@
         <v>0</v>
       </c>
       <c r="V114">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W114">
         <v>0.72</v>
@@ -11300,7 +11330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:31">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -11308,7 +11338,7 @@
         <v>55670</v>
       </c>
       <c r="C115">
-        <v>4.61</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D115">
         <v>99.27</v>
@@ -11380,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>513.5700000000001</v>
+        <v>513.57000000000005</v>
       </c>
       <c r="AB115">
         <v>756.48</v>
@@ -11395,7 +11425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:31">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -11406,7 +11436,7 @@
         <v>3.02</v>
       </c>
       <c r="D116">
-        <v>67.01000000000001</v>
+        <v>67.010000000000005</v>
       </c>
       <c r="E116">
         <v>70.63</v>
@@ -11454,7 +11484,7 @@
         <v>66.92</v>
       </c>
       <c r="T116">
-        <v>34.3</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="U116">
         <v>0</v>
@@ -11463,7 +11493,7 @@
         <v>0.42</v>
       </c>
       <c r="W116">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X116">
         <v>0</v>
@@ -11475,7 +11505,7 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>538.7</v>
+        <v>538.70000000000005</v>
       </c>
       <c r="AB116">
         <v>910.39</v>
@@ -11490,7 +11520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:31">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -11525,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="L117">
-        <v>1092.91</v>
+        <v>1092.9100000000001</v>
       </c>
       <c r="M117">
         <v>946.45</v>
@@ -11543,10 +11573,10 @@
         <v>11329</v>
       </c>
       <c r="R117">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="S117">
-        <v>73.98999999999999</v>
+        <v>73.989999999999995</v>
       </c>
       <c r="T117">
         <v>34.78</v>
@@ -11585,7 +11615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:31">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -11650,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="V118">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="W118">
         <v>0.86</v>
@@ -11680,7 +11710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="119" spans="1:31">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -11694,7 +11724,7 @@
         <v>60.29</v>
       </c>
       <c r="E119">
-        <v>73.56999999999999</v>
+        <v>73.569999999999993</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -11703,7 +11733,7 @@
         <v>0.71</v>
       </c>
       <c r="H119">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -11715,7 +11745,7 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>1230.86</v>
+        <v>1230.8599999999999</v>
       </c>
       <c r="M119">
         <v>632.72</v>
@@ -11775,7 +11805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="120" spans="1:31">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -11783,7 +11813,7 @@
         <v>67707</v>
       </c>
       <c r="C120">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="D120">
         <v>27.53</v>
@@ -11870,7 +11900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:31">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -11878,10 +11908,10 @@
         <v>46727</v>
       </c>
       <c r="C121">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="D121">
-        <v>74.54000000000001</v>
+        <v>74.540000000000006</v>
       </c>
       <c r="E121">
         <v>42.03</v>
@@ -11908,7 +11938,7 @@
         <v>358.75</v>
       </c>
       <c r="M121">
-        <v>611.0599999999999</v>
+        <v>611.05999999999995</v>
       </c>
       <c r="N121" t="s">
         <v>31</v>
@@ -11923,7 +11953,7 @@
         <v>39825</v>
       </c>
       <c r="R121">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="S121">
         <v>72.03</v>
@@ -11965,7 +11995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:31">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -11976,7 +12006,7 @@
         <v>1.24</v>
       </c>
       <c r="D122">
-        <v>83.84999999999999</v>
+        <v>83.85</v>
       </c>
       <c r="E122">
         <v>96.12</v>
@@ -12060,7 +12090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:31">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -12155,7 +12185,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:31">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -12163,7 +12193,7 @@
         <v>63161</v>
       </c>
       <c r="C124">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="D124">
         <v>38.99</v>
@@ -12208,7 +12238,7 @@
         <v>52964</v>
       </c>
       <c r="R124">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="S124">
         <v>35.01</v>
@@ -12238,7 +12268,7 @@
         <v>482.25</v>
       </c>
       <c r="AB124">
-        <v>731.4400000000001</v>
+        <v>731.44</v>
       </c>
       <c r="AC124" t="s">
         <v>31</v>
@@ -12250,7 +12280,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="125" spans="1:31">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -12258,7 +12288,7 @@
         <v>252173</v>
       </c>
       <c r="C125">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D125">
         <v>75.12</v>
@@ -12285,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="L125">
-        <v>829.5599999999999</v>
+        <v>829.56</v>
       </c>
       <c r="M125">
         <v>535.37</v>
@@ -12345,7 +12375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:31">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -12383,7 +12413,7 @@
         <v>1148.22</v>
       </c>
       <c r="M126">
-        <v>804.3099999999999</v>
+        <v>804.31</v>
       </c>
       <c r="N126" t="s">
         <v>31</v>
@@ -12425,7 +12455,7 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>1145.1</v>
+        <v>1145.0999999999999</v>
       </c>
       <c r="AB126">
         <v>804.26</v>
@@ -12440,7 +12470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:31">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -12454,7 +12484,7 @@
         <v>80.25</v>
       </c>
       <c r="E127">
-        <v>96.48999999999999</v>
+        <v>96.49</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -12475,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="L127">
-        <v>1197.85</v>
+        <v>1197.8499999999999</v>
       </c>
       <c r="M127">
         <v>583.47</v>
@@ -12523,7 +12553,7 @@
         <v>1217.47</v>
       </c>
       <c r="AB127">
-        <v>579.3</v>
+        <v>579.29999999999995</v>
       </c>
       <c r="AC127" t="s">
         <v>31</v>
@@ -12535,7 +12565,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:31">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -12603,7 +12633,7 @@
         <v>0.45</v>
       </c>
       <c r="W128">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X128">
         <v>0</v>
@@ -12630,7 +12660,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:31">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -12668,7 +12698,7 @@
         <v>302.61</v>
       </c>
       <c r="M129">
-        <v>629.92</v>
+        <v>629.91999999999996</v>
       </c>
       <c r="N129" t="s">
         <v>31</v>
@@ -12710,7 +12740,7 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>301.84</v>
+        <v>301.83999999999997</v>
       </c>
       <c r="AB129">
         <v>631.59</v>
@@ -12725,7 +12755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:31">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -12745,7 +12775,7 @@
         <v>0</v>
       </c>
       <c r="G130">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H130">
         <v>0.93</v>
@@ -12778,13 +12808,13 @@
         <v>113689</v>
       </c>
       <c r="R130">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="S130">
         <v>44.45</v>
       </c>
       <c r="T130">
-        <v>34.02</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="U130">
         <v>0</v>
@@ -12805,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="AA130">
-        <v>262.66</v>
+        <v>262.66000000000003</v>
       </c>
       <c r="AB130">
         <v>325.24</v>
@@ -12820,7 +12850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:31">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -12831,7 +12861,7 @@
         <v>2.52</v>
       </c>
       <c r="D131">
-        <v>75.09999999999999</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="E131">
         <v>76.7</v>
@@ -12843,7 +12873,7 @@
         <v>0.06</v>
       </c>
       <c r="H131">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -12915,7 +12945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:31">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -12923,7 +12953,7 @@
         <v>148988</v>
       </c>
       <c r="C132">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D132">
         <v>114.25</v>
@@ -12938,7 +12968,7 @@
         <v>0.44</v>
       </c>
       <c r="H132">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -12995,7 +13025,7 @@
         <v>0</v>
       </c>
       <c r="AA132">
-        <v>602.0599999999999</v>
+        <v>602.05999999999995</v>
       </c>
       <c r="AB132">
         <v>249.2</v>
@@ -13010,7 +13040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:31">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -13063,7 +13093,7 @@
         <v>58781</v>
       </c>
       <c r="R133">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="S133">
         <v>76.33</v>
@@ -13105,7 +13135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:31">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -13200,7 +13230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:31">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -13295,7 +13325,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:31">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -13315,7 +13345,7 @@
         <v>0</v>
       </c>
       <c r="G136">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H136">
         <v>0.72</v>
@@ -13390,7 +13420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:31">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -13425,7 +13455,7 @@
         <v>0</v>
       </c>
       <c r="L137">
-        <v>263.4</v>
+        <v>263.39999999999998</v>
       </c>
       <c r="M137">
         <v>772.91</v>
@@ -13485,7 +13515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:31">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -13520,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="L138">
-        <v>512.17</v>
+        <v>512.16999999999996</v>
       </c>
       <c r="M138">
         <v>346.71</v>
@@ -13538,7 +13568,7 @@
         <v>60162</v>
       </c>
       <c r="R138">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="S138">
         <v>126.49</v>
@@ -13580,7 +13610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:31">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -13594,7 +13624,7 @@
         <v>52.24</v>
       </c>
       <c r="E139">
-        <v>96.06999999999999</v>
+        <v>96.07</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -13639,13 +13669,13 @@
         <v>52.14</v>
       </c>
       <c r="T139">
-        <v>79.20999999999999</v>
+        <v>79.209999999999994</v>
       </c>
       <c r="U139">
         <v>0</v>
       </c>
       <c r="V139">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W139">
         <v>0.72</v>
@@ -13675,7 +13705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:31">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -13686,7 +13716,7 @@
         <v>2.25</v>
       </c>
       <c r="D140">
-        <v>70.81999999999999</v>
+        <v>70.819999999999993</v>
       </c>
       <c r="E140">
         <v>144.13</v>
@@ -13698,7 +13728,7 @@
         <v>0.44</v>
       </c>
       <c r="H140">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -13731,7 +13761,7 @@
         <v>2.15</v>
       </c>
       <c r="S140">
-        <v>69.09999999999999</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="T140">
         <v>79.91</v>
@@ -13743,7 +13773,7 @@
         <v>0.44</v>
       </c>
       <c r="W140">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X140">
         <v>0</v>
@@ -13755,10 +13785,10 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>649.4299999999999</v>
+        <v>649.42999999999995</v>
       </c>
       <c r="AB140">
-        <v>783.3200000000001</v>
+        <v>783.32</v>
       </c>
       <c r="AC140" t="s">
         <v>31</v>
@@ -13770,7 +13800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:31">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -13853,7 +13883,7 @@
         <v>797.53</v>
       </c>
       <c r="AB141">
-        <v>533.6900000000001</v>
+        <v>533.69000000000005</v>
       </c>
       <c r="AC141" t="s">
         <v>31</v>
@@ -13865,7 +13895,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:31">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -13885,7 +13915,7 @@
         <v>0</v>
       </c>
       <c r="G142">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H142">
         <v>0.45</v>
@@ -13924,7 +13954,7 @@
         <v>48.79</v>
       </c>
       <c r="T142">
-        <v>66.54000000000001</v>
+        <v>66.540000000000006</v>
       </c>
       <c r="U142">
         <v>0</v>
@@ -13960,7 +13990,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:31">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -13995,7 +14025,7 @@
         <v>0</v>
       </c>
       <c r="L143">
-        <v>1105.66</v>
+        <v>1105.6600000000001</v>
       </c>
       <c r="M143">
         <v>391.37</v>
@@ -14055,7 +14085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:31">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -14090,7 +14120,7 @@
         <v>0</v>
       </c>
       <c r="L144">
-        <v>270.66</v>
+        <v>270.66000000000003</v>
       </c>
       <c r="M144">
         <v>327.81</v>
@@ -14150,7 +14180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:31">
+    <row r="145" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -14161,10 +14191,10 @@
         <v>1.36</v>
       </c>
       <c r="D145">
-        <v>73.93000000000001</v>
+        <v>73.930000000000007</v>
       </c>
       <c r="E145">
-        <v>72.59999999999999</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -14173,7 +14203,7 @@
         <v>0.31</v>
       </c>
       <c r="H145">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -14245,7 +14275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:31">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -14340,7 +14370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:31">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -14435,7 +14465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:31">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -14515,7 +14545,7 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>735.5599999999999</v>
+        <v>735.56</v>
       </c>
       <c r="AB148">
         <v>391.75</v>
@@ -14530,7 +14560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:31">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -14625,7 +14655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="150" spans="1:31">
+    <row r="150" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -14648,7 +14678,7 @@
         <v>0.19</v>
       </c>
       <c r="H150">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -14660,7 +14690,7 @@
         <v>0</v>
       </c>
       <c r="L150">
-        <v>1129.87</v>
+        <v>1129.8699999999999</v>
       </c>
       <c r="M150">
         <v>268.02</v>
@@ -14684,7 +14714,7 @@
         <v>41.46</v>
       </c>
       <c r="T150">
-        <v>32.13</v>
+        <v>32.130000000000003</v>
       </c>
       <c r="U150">
         <v>0</v>
@@ -14705,7 +14735,7 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>1128.09</v>
+        <v>1128.0899999999999</v>
       </c>
       <c r="AB150">
         <v>252.51</v>
@@ -14720,7 +14750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:31">
+    <row r="151" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -14815,7 +14845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:31">
+    <row r="152" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -14868,7 +14898,7 @@
         <v>148348</v>
       </c>
       <c r="R152">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="S152">
         <v>67.7</v>
@@ -14895,7 +14925,7 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>594.2</v>
+        <v>594.20000000000005</v>
       </c>
       <c r="AB152">
         <v>552.53</v>
@@ -14910,7 +14940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:31">
+    <row r="153" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -14969,7 +14999,7 @@
         <v>72.62</v>
       </c>
       <c r="T153">
-        <v>92.18000000000001</v>
+        <v>92.18</v>
       </c>
       <c r="U153">
         <v>0</v>
@@ -14978,7 +15008,7 @@
         <v>0.93</v>
       </c>
       <c r="W153">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X153">
         <v>0</v>
@@ -15005,7 +15035,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:31">
+    <row r="154" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -15016,7 +15046,7 @@
         <v>3.49</v>
       </c>
       <c r="D154">
-        <v>77.43000000000001</v>
+        <v>77.430000000000007</v>
       </c>
       <c r="E154">
         <v>107.86</v>
@@ -15061,10 +15091,10 @@
         <v>6.42</v>
       </c>
       <c r="S154">
-        <v>77.23999999999999</v>
+        <v>77.239999999999995</v>
       </c>
       <c r="T154">
-        <v>40.7</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="U154">
         <v>0</v>
@@ -15100,7 +15130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:31">
+    <row r="155" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -15195,7 +15225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:31">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -15209,7 +15239,7 @@
         <v>58.83</v>
       </c>
       <c r="E156">
-        <v>143.27</v>
+        <v>143.27000000000001</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -15230,7 +15260,7 @@
         <v>0</v>
       </c>
       <c r="L156">
-        <v>1044.64</v>
+        <v>1044.6400000000001</v>
       </c>
       <c r="M156">
         <v>782.89</v>
@@ -15290,7 +15320,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="157" spans="1:31">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -15370,7 +15400,7 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>1132.1</v>
+        <v>1132.0999999999999</v>
       </c>
       <c r="AB157">
         <v>598.38</v>
@@ -15385,7 +15415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:31">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -15396,10 +15426,10 @@
         <v>1.35</v>
       </c>
       <c r="D158">
-        <v>40.27</v>
+        <v>40.270000000000003</v>
       </c>
       <c r="E158">
-        <v>66.45999999999999</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -15423,7 +15453,7 @@
         <v>1335.09</v>
       </c>
       <c r="M158">
-        <v>877.3200000000001</v>
+        <v>877.32</v>
       </c>
       <c r="N158" t="s">
         <v>30</v>
@@ -15480,7 +15510,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:31">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -15575,7 +15605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:31">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -15586,10 +15616,10 @@
         <v>3.89</v>
       </c>
       <c r="D160">
-        <v>39.05</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="E160">
-        <v>158.45</v>
+        <v>158.44999999999999</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -15628,13 +15658,13 @@
         <v>106444</v>
       </c>
       <c r="R160">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="S160">
-        <v>33.63</v>
+        <v>33.630000000000003</v>
       </c>
       <c r="T160">
-        <v>64.45999999999999</v>
+        <v>64.459999999999994</v>
       </c>
       <c r="U160">
         <v>0</v>
@@ -15670,7 +15700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:31">
+    <row r="161" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -15705,10 +15735,10 @@
         <v>0</v>
       </c>
       <c r="L161">
-        <v>628.9299999999999</v>
+        <v>628.92999999999995</v>
       </c>
       <c r="M161">
-        <v>578.05</v>
+        <v>578.04999999999995</v>
       </c>
       <c r="N161" t="s">
         <v>30</v>
@@ -15726,7 +15756,7 @@
         <v>4.58</v>
       </c>
       <c r="S161">
-        <v>84.68000000000001</v>
+        <v>84.68</v>
       </c>
       <c r="T161">
         <v>140.51</v>
@@ -15765,7 +15795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="162" spans="1:31">
+    <row r="162" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -15860,7 +15890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="163" spans="1:31">
+    <row r="163" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -15955,7 +15985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:31">
+    <row r="164" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -16050,7 +16080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:31">
+    <row r="165" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -16145,7 +16175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:31">
+    <row r="166" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -16153,13 +16183,13 @@
         <v>149584</v>
       </c>
       <c r="C166">
-        <v>4.65</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="D166">
         <v>94.47</v>
       </c>
       <c r="E166">
-        <v>158.05</v>
+        <v>158.05000000000001</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -16204,7 +16234,7 @@
         <v>86.67</v>
       </c>
       <c r="T166">
-        <v>79.23999999999999</v>
+        <v>79.239999999999995</v>
       </c>
       <c r="U166">
         <v>0</v>
@@ -16240,7 +16270,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:31">
+    <row r="167" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -16248,7 +16278,7 @@
         <v>120395</v>
       </c>
       <c r="C167">
-        <v>8.279999999999999</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="D167">
         <v>86.17</v>
@@ -16335,7 +16365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:31">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -16391,7 +16421,7 @@
         <v>2.52</v>
       </c>
       <c r="S168">
-        <v>69.56999999999999</v>
+        <v>69.569999999999993</v>
       </c>
       <c r="T168">
         <v>47.22</v>
@@ -16430,7 +16460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:31">
+    <row r="169" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -16525,7 +16555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:31">
+    <row r="170" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -16563,7 +16593,7 @@
         <v>373.33</v>
       </c>
       <c r="M170">
-        <v>642.3200000000001</v>
+        <v>642.32000000000005</v>
       </c>
       <c r="N170" t="s">
         <v>30</v>
@@ -16620,7 +16650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:31">
+    <row r="171" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -16634,7 +16664,7 @@
         <v>63.72</v>
       </c>
       <c r="E171">
-        <v>78.34999999999999</v>
+        <v>78.349999999999994</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -16658,7 +16688,7 @@
         <v>397.38</v>
       </c>
       <c r="M171">
-        <v>872.4400000000001</v>
+        <v>872.44</v>
       </c>
       <c r="N171" t="s">
         <v>30</v>
@@ -16715,7 +16745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:31">
+    <row r="172" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -16810,7 +16840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:31">
+    <row r="173" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -16890,7 +16920,7 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>564.8099999999999</v>
+        <v>564.80999999999995</v>
       </c>
       <c r="AB173">
         <v>639.24</v>
@@ -16905,7 +16935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:31">
+    <row r="174" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -16916,7 +16946,7 @@
         <v>3.7</v>
       </c>
       <c r="D174">
-        <v>64.43000000000001</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="E174">
         <v>126.44</v>
@@ -17000,7 +17030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:31">
+    <row r="175" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -17011,7 +17041,7 @@
         <v>6.77</v>
       </c>
       <c r="D175">
-        <v>66.48999999999999</v>
+        <v>66.489999999999995</v>
       </c>
       <c r="E175">
         <v>112.01</v>
@@ -17035,7 +17065,7 @@
         <v>0</v>
       </c>
       <c r="L175">
-        <v>1059.63</v>
+        <v>1059.6300000000001</v>
       </c>
       <c r="M175">
         <v>450.54</v>
@@ -17095,7 +17125,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:31">
+    <row r="176" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -17106,7 +17136,7 @@
         <v>6.25</v>
       </c>
       <c r="D176">
-        <v>83.73999999999999</v>
+        <v>83.74</v>
       </c>
       <c r="E176">
         <v>112.39</v>
@@ -17133,7 +17163,7 @@
         <v>561.48</v>
       </c>
       <c r="M176">
-        <v>673.6799999999999</v>
+        <v>673.68</v>
       </c>
       <c r="N176" t="s">
         <v>30</v>
@@ -17178,7 +17208,7 @@
         <v>478.26</v>
       </c>
       <c r="AB176">
-        <v>648.33</v>
+        <v>648.33000000000004</v>
       </c>
       <c r="AC176" t="s">
         <v>30</v>
@@ -17190,7 +17220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:31">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -17201,7 +17231,7 @@
         <v>4.47</v>
       </c>
       <c r="D177">
-        <v>81.76000000000001</v>
+        <v>81.760000000000005</v>
       </c>
       <c r="E177">
         <v>182.08</v>
@@ -17225,7 +17255,7 @@
         <v>0</v>
       </c>
       <c r="L177">
-        <v>950.9299999999999</v>
+        <v>950.93</v>
       </c>
       <c r="M177">
         <v>490.28</v>
@@ -17285,7 +17315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="1:31">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -17380,7 +17410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:31">
+    <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -17391,10 +17421,10 @@
         <v>2.1</v>
       </c>
       <c r="D179">
-        <v>37.77</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="E179">
-        <v>87.93000000000001</v>
+        <v>87.93</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -17475,7 +17505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:31">
+    <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -17489,7 +17519,7 @@
         <v>47.7</v>
       </c>
       <c r="E180">
-        <v>139.3</v>
+        <v>139.30000000000001</v>
       </c>
       <c r="F180">
         <v>0</v>
@@ -17513,7 +17543,7 @@
         <v>473.24</v>
       </c>
       <c r="M180">
-        <v>726.1900000000001</v>
+        <v>726.19</v>
       </c>
       <c r="N180" t="s">
         <v>30</v>
@@ -17570,7 +17600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:31">
+    <row r="181" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -17584,7 +17614,7 @@
         <v>61.17</v>
       </c>
       <c r="E181">
-        <v>89.79000000000001</v>
+        <v>89.79</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -17593,7 +17623,7 @@
         <v>0.93</v>
       </c>
       <c r="H181">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -17638,7 +17668,7 @@
         <v>0.86</v>
       </c>
       <c r="W181">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X181">
         <v>0</v>
@@ -17665,7 +17695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="182" spans="1:31">
+    <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -17748,7 +17778,7 @@
         <v>870.52</v>
       </c>
       <c r="AB182">
-        <v>597.2</v>
+        <v>597.20000000000005</v>
       </c>
       <c r="AC182" t="s">
         <v>30</v>
@@ -17760,7 +17790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:31">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -17771,7 +17801,7 @@
         <v>7.01</v>
       </c>
       <c r="D183">
-        <v>77.84999999999999</v>
+        <v>77.849999999999994</v>
       </c>
       <c r="E183">
         <v>113.49</v>
@@ -17855,7 +17885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:31">
+    <row r="184" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -17866,7 +17896,7 @@
         <v>6.34</v>
       </c>
       <c r="D184">
-        <v>69.76000000000001</v>
+        <v>69.760000000000005</v>
       </c>
       <c r="E184">
         <v>129.29</v>
@@ -17890,7 +17920,7 @@
         <v>0</v>
       </c>
       <c r="L184">
-        <v>1070.39</v>
+        <v>1070.3900000000001</v>
       </c>
       <c r="M184">
         <v>371.42</v>
@@ -17950,7 +17980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:31">
+    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -18045,7 +18075,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:31">
+    <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -18065,7 +18095,7 @@
         <v>0</v>
       </c>
       <c r="G186">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H186">
         <v>0.06</v>
@@ -18140,7 +18170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:31">
+    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -18196,7 +18226,7 @@
         <v>5.66</v>
       </c>
       <c r="S187">
-        <v>68.73999999999999</v>
+        <v>68.739999999999995</v>
       </c>
       <c r="T187">
         <v>45.6</v>
@@ -18235,7 +18265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:31">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -18273,7 +18303,7 @@
         <v>955.76</v>
       </c>
       <c r="M188">
-        <v>546.6900000000001</v>
+        <v>546.69000000000005</v>
       </c>
       <c r="N188" t="s">
         <v>30</v>
@@ -18303,7 +18333,7 @@
         <v>0.93</v>
       </c>
       <c r="W188">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X188">
         <v>0</v>
@@ -18330,7 +18360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:31">
+    <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -18365,7 +18395,7 @@
         <v>0</v>
       </c>
       <c r="L189">
-        <v>789.5700000000001</v>
+        <v>789.57</v>
       </c>
       <c r="M189">
         <v>913.29</v>
@@ -18389,7 +18419,7 @@
         <v>31.58</v>
       </c>
       <c r="T189">
-        <v>74.81999999999999</v>
+        <v>74.819999999999993</v>
       </c>
       <c r="U189">
         <v>0</v>
@@ -18425,7 +18455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="190" spans="1:31">
+    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -18520,7 +18550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="191" spans="1:31">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -18573,10 +18603,10 @@
         <v>197168</v>
       </c>
       <c r="R191">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="S191">
-        <v>78.54000000000001</v>
+        <v>78.540000000000006</v>
       </c>
       <c r="T191">
         <v>43.91</v>
@@ -18615,7 +18645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:31">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -18623,7 +18653,7 @@
         <v>89454</v>
       </c>
       <c r="C192">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="D192">
         <v>67.31</v>
@@ -18680,7 +18710,7 @@
         <v>0</v>
       </c>
       <c r="V192">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W192">
         <v>0.06</v>
@@ -18710,7 +18740,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="193" spans="1:31">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -18790,10 +18820,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>1248.87</v>
+        <v>1248.8699999999999</v>
       </c>
       <c r="AB193">
-        <v>545.3</v>
+        <v>545.29999999999995</v>
       </c>
       <c r="AC193" t="s">
         <v>30</v>
@@ -18805,7 +18835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:31">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -18816,7 +18846,7 @@
         <v>4.74</v>
       </c>
       <c r="D194">
-        <v>74.31999999999999</v>
+        <v>74.319999999999993</v>
       </c>
       <c r="E194">
         <v>124.83</v>
@@ -18861,7 +18891,7 @@
         <v>5.33</v>
       </c>
       <c r="S194">
-        <v>69.34999999999999</v>
+        <v>69.349999999999994</v>
       </c>
       <c r="T194">
         <v>46.48</v>
@@ -18900,7 +18930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:31">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -18935,7 +18965,7 @@
         <v>0</v>
       </c>
       <c r="L195">
-        <v>318.91</v>
+        <v>318.91000000000003</v>
       </c>
       <c r="M195">
         <v>298.31</v>
@@ -18995,7 +19025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:31">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -19003,7 +19033,7 @@
         <v>127963</v>
       </c>
       <c r="C196">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="D196">
         <v>57.09</v>
@@ -19063,7 +19093,7 @@
         <v>0.86</v>
       </c>
       <c r="W196">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X196">
         <v>0</v>
@@ -19075,7 +19105,7 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>144.64</v>
+        <v>144.63999999999999</v>
       </c>
       <c r="AB196">
         <v>930.75</v>
@@ -19090,7 +19120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:31">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -19128,7 +19158,7 @@
         <v>235</v>
       </c>
       <c r="M197">
-        <v>635.5700000000001</v>
+        <v>635.57000000000005</v>
       </c>
       <c r="N197" t="s">
         <v>30</v>
@@ -19173,7 +19203,7 @@
         <v>235.11</v>
       </c>
       <c r="AB197">
-        <v>638.3200000000001</v>
+        <v>638.32000000000005</v>
       </c>
       <c r="AC197" t="s">
         <v>30</v>
@@ -19185,7 +19215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:31">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -19199,7 +19229,7 @@
         <v>72.77</v>
       </c>
       <c r="E198">
-        <v>159.77</v>
+        <v>159.77000000000001</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -19265,7 +19295,7 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>569.55</v>
+        <v>569.54999999999995</v>
       </c>
       <c r="AB198">
         <v>843.75</v>
@@ -19280,7 +19310,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:31">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -19288,7 +19318,7 @@
         <v>58901</v>
       </c>
       <c r="C199">
-        <v>4.27</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="D199">
         <v>90.23</v>
@@ -19375,7 +19405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:31">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -19431,7 +19461,7 @@
         <v>5.79</v>
       </c>
       <c r="S200">
-        <v>75.59999999999999</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="T200">
         <v>50.28</v>
@@ -19470,7 +19500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:31">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -19508,7 +19538,7 @@
         <v>510.07</v>
       </c>
       <c r="M201">
-        <v>567.17</v>
+        <v>567.16999999999996</v>
       </c>
       <c r="N201" t="s">
         <v>30</v>
@@ -19523,7 +19553,7 @@
         <v>89721</v>
       </c>
       <c r="R201">
-        <v>4.98</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="S201">
         <v>85.8</v>
@@ -19553,7 +19583,7 @@
         <v>516.12</v>
       </c>
       <c r="AB201">
-        <v>568.6799999999999</v>
+        <v>568.67999999999995</v>
       </c>
       <c r="AC201" t="s">
         <v>30</v>
@@ -19565,7 +19595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:31">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -19645,7 +19675,7 @@
         <v>0</v>
       </c>
       <c r="AA202">
-        <v>665.9299999999999</v>
+        <v>665.93</v>
       </c>
       <c r="AB202">
         <v>298.26</v>
@@ -19660,7 +19690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:31">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -19755,7 +19785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204" spans="1:31">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -19763,7 +19793,7 @@
         <v>176084</v>
       </c>
       <c r="C204">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D204">
         <v>66.88</v>
@@ -19793,7 +19823,7 @@
         <v>301.82</v>
       </c>
       <c r="M204">
-        <v>759.8099999999999</v>
+        <v>759.81</v>
       </c>
       <c r="N204" t="s">
         <v>30</v>
@@ -19808,7 +19838,7 @@
         <v>143343</v>
       </c>
       <c r="R204">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="S204">
         <v>64.06</v>
@@ -19835,7 +19865,7 @@
         <v>0</v>
       </c>
       <c r="AA204">
-        <v>298.4</v>
+        <v>298.39999999999998</v>
       </c>
       <c r="AB204">
         <v>760.83</v>
@@ -19850,7 +19880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:31">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -19906,7 +19936,7 @@
         <v>9.02</v>
       </c>
       <c r="S205">
-        <v>81.95999999999999</v>
+        <v>81.96</v>
       </c>
       <c r="T205">
         <v>52.82</v>
@@ -19945,7 +19975,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:31">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -19998,7 +20028,7 @@
         <v>69333</v>
       </c>
       <c r="R206">
-        <v>8.619999999999999</v>
+        <v>8.6199999999999992</v>
       </c>
       <c r="S206">
         <v>81.48</v>
@@ -20040,7 +20070,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:31">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -20135,7 +20165,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:31">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -20230,7 +20260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:31">
+    <row r="209" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -20244,7 +20274,7 @@
         <v>72.81</v>
       </c>
       <c r="E209">
-        <v>92.70999999999999</v>
+        <v>92.71</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -20286,7 +20316,7 @@
         <v>2.67</v>
       </c>
       <c r="S209">
-        <v>75.95999999999999</v>
+        <v>75.959999999999994</v>
       </c>
       <c r="T209">
         <v>44.78</v>
@@ -20298,7 +20328,7 @@
         <v>0.31</v>
       </c>
       <c r="W209">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X209">
         <v>0</v>
@@ -20325,7 +20355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:31">
+    <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -20333,13 +20363,13 @@
         <v>170992</v>
       </c>
       <c r="C210">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="D210">
-        <v>75.68000000000001</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="E210">
-        <v>134.2</v>
+        <v>134.19999999999999</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -20381,7 +20411,7 @@
         <v>2.46</v>
       </c>
       <c r="S210">
-        <v>76.26000000000001</v>
+        <v>76.260000000000005</v>
       </c>
       <c r="T210">
         <v>72.58</v>
@@ -20420,7 +20450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:31">
+    <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -20458,7 +20488,7 @@
         <v>720.16</v>
       </c>
       <c r="M211">
-        <v>664.1799999999999</v>
+        <v>664.18</v>
       </c>
       <c r="N211" t="s">
         <v>31</v>
@@ -20515,7 +20545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:31">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -20595,7 +20625,7 @@
         <v>0</v>
       </c>
       <c r="AA212">
-        <v>1133.59</v>
+        <v>1133.5899999999999</v>
       </c>
       <c r="AB212">
         <v>933.99</v>
@@ -20610,7 +20640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="213" spans="1:31">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -20648,7 +20678,7 @@
         <v>1192.68</v>
       </c>
       <c r="M213">
-        <v>731.1799999999999</v>
+        <v>731.18</v>
       </c>
       <c r="N213" t="s">
         <v>31</v>
@@ -20666,7 +20696,7 @@
         <v>3.82</v>
       </c>
       <c r="S213">
-        <v>97.18000000000001</v>
+        <v>97.18</v>
       </c>
       <c r="T213">
         <v>63.42</v>
@@ -20678,7 +20708,7 @@
         <v>0.31</v>
       </c>
       <c r="W213">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X213">
         <v>0</v>
@@ -20690,7 +20720,7 @@
         <v>0</v>
       </c>
       <c r="AA213">
-        <v>1130.41</v>
+        <v>1130.4100000000001</v>
       </c>
       <c r="AB213">
         <v>631.35</v>
@@ -20705,7 +20735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="214" spans="1:31">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -20719,7 +20749,7 @@
         <v>53.44</v>
       </c>
       <c r="E214">
-        <v>83.06999999999999</v>
+        <v>83.07</v>
       </c>
       <c r="F214">
         <v>0</v>
@@ -20800,7 +20830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:31">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -20835,7 +20865,7 @@
         <v>0</v>
       </c>
       <c r="L215">
-        <v>549.42</v>
+        <v>549.41999999999996</v>
       </c>
       <c r="M215">
         <v>472.4</v>
@@ -20895,7 +20925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:31">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -20975,7 +21005,7 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>658.4299999999999</v>
+        <v>658.43</v>
       </c>
       <c r="AB216">
         <v>764.96</v>
@@ -20990,7 +21020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:31">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -21004,13 +21034,13 @@
         <v>127.56</v>
       </c>
       <c r="E217">
-        <v>156.52</v>
+        <v>156.52000000000001</v>
       </c>
       <c r="F217">
         <v>0</v>
       </c>
       <c r="G217">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H217">
         <v>0.42</v>
@@ -21025,7 +21055,7 @@
         <v>0</v>
       </c>
       <c r="L217">
-        <v>585.8200000000001</v>
+        <v>585.82000000000005</v>
       </c>
       <c r="M217">
         <v>614.01</v>
@@ -21043,7 +21073,7 @@
         <v>210648</v>
       </c>
       <c r="R217">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="S217">
         <v>99.39</v>
@@ -21058,7 +21088,7 @@
         <v>0.42</v>
       </c>
       <c r="W217">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X217">
         <v>0</v>
@@ -21085,7 +21115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:31">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -21093,7 +21123,7 @@
         <v>98836</v>
       </c>
       <c r="C218">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="D218">
         <v>84.02</v>
@@ -21105,7 +21135,7 @@
         <v>0</v>
       </c>
       <c r="G218">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H218">
         <v>0.93</v>
@@ -21180,7 +21210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:31">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -21191,7 +21221,7 @@
         <v>2.76</v>
       </c>
       <c r="D219">
-        <v>80.23999999999999</v>
+        <v>80.239999999999995</v>
       </c>
       <c r="E219">
         <v>92.92</v>
@@ -21248,7 +21278,7 @@
         <v>0.44</v>
       </c>
       <c r="W219">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X219">
         <v>0</v>
@@ -21275,7 +21305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:31">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -21289,7 +21319,7 @@
         <v>80.41</v>
       </c>
       <c r="E220">
-        <v>147.08</v>
+        <v>147.08000000000001</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -21310,7 +21340,7 @@
         <v>0</v>
       </c>
       <c r="L220">
-        <v>577.9400000000001</v>
+        <v>577.94000000000005</v>
       </c>
       <c r="M220">
         <v>886.36</v>
@@ -21334,7 +21364,7 @@
         <v>59.32</v>
       </c>
       <c r="T220">
-        <v>72.18000000000001</v>
+        <v>72.180000000000007</v>
       </c>
       <c r="U220">
         <v>0</v>
@@ -21355,7 +21385,7 @@
         <v>0</v>
       </c>
       <c r="AA220">
-        <v>533.6799999999999</v>
+        <v>533.67999999999995</v>
       </c>
       <c r="AB220">
         <v>1009.34</v>
@@ -21370,7 +21400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:31">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -21378,7 +21408,7 @@
         <v>123715</v>
       </c>
       <c r="C221">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D221">
         <v>94.73</v>
@@ -21390,7 +21420,7 @@
         <v>0</v>
       </c>
       <c r="G221">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H221">
         <v>0.44</v>
@@ -21465,7 +21495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:31">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -21521,7 +21551,7 @@
         <v>4.34</v>
       </c>
       <c r="S222">
-        <v>64.18000000000001</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="T222">
         <v>60.36</v>
@@ -21530,7 +21560,7 @@
         <v>0</v>
       </c>
       <c r="V222">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W222">
         <v>0.71</v>
@@ -21560,7 +21590,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:31">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -21574,7 +21604,7 @@
         <v>50.61</v>
       </c>
       <c r="E223">
-        <v>145.58</v>
+        <v>145.58000000000001</v>
       </c>
       <c r="F223">
         <v>0</v>
@@ -21655,7 +21685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:31">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -21750,7 +21780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:31">
+    <row r="225" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -21833,7 +21863,7 @@
         <v>277.3</v>
       </c>
       <c r="AB225">
-        <v>671.8200000000001</v>
+        <v>671.82</v>
       </c>
       <c r="AC225" t="s">
         <v>31</v>
@@ -21845,7 +21875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:31">
+    <row r="226" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -21904,7 +21934,7 @@
         <v>79.56</v>
       </c>
       <c r="T226">
-        <v>66.06999999999999</v>
+        <v>66.069999999999993</v>
       </c>
       <c r="U226">
         <v>0</v>
@@ -21940,7 +21970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:31">
+    <row r="227" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -21951,7 +21981,7 @@
         <v>2.61</v>
       </c>
       <c r="D227">
-        <v>75.40000000000001</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="E227">
         <v>122.2</v>
@@ -21978,7 +22008,7 @@
         <v>941.52</v>
       </c>
       <c r="M227">
-        <v>779.3200000000001</v>
+        <v>779.32</v>
       </c>
       <c r="N227" t="s">
         <v>31</v>
@@ -21993,7 +22023,7 @@
         <v>117300</v>
       </c>
       <c r="R227">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="S227">
         <v>102.53</v>
@@ -22005,7 +22035,7 @@
         <v>0</v>
       </c>
       <c r="V227">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W227">
         <v>0.71</v>
@@ -22023,7 +22053,7 @@
         <v>838.83</v>
       </c>
       <c r="AB227">
-        <v>795.5599999999999</v>
+        <v>795.56</v>
       </c>
       <c r="AC227" t="s">
         <v>31</v>
@@ -22035,7 +22065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:31">
+    <row r="228" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -22049,7 +22079,7 @@
         <v>114.41</v>
       </c>
       <c r="E228">
-        <v>149.58</v>
+        <v>149.58000000000001</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -22058,7 +22088,7 @@
         <v>0.42</v>
       </c>
       <c r="H228">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I228">
         <v>0</v>
@@ -22073,7 +22103,7 @@
         <v>934.79</v>
       </c>
       <c r="M228">
-        <v>842.9299999999999</v>
+        <v>842.93</v>
       </c>
       <c r="N228" t="s">
         <v>31</v>
@@ -22130,7 +22160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:31">
+    <row r="229" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -22138,10 +22168,10 @@
         <v>90039</v>
       </c>
       <c r="C229">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="D229">
-        <v>78.06999999999999</v>
+        <v>78.069999999999993</v>
       </c>
       <c r="E229">
         <v>140.51</v>
@@ -22186,16 +22216,16 @@
         <v>2.16</v>
       </c>
       <c r="S229">
-        <v>77.56999999999999</v>
+        <v>77.569999999999993</v>
       </c>
       <c r="T229">
-        <v>91.15000000000001</v>
+        <v>91.15</v>
       </c>
       <c r="U229">
         <v>0</v>
       </c>
       <c r="V229">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W229">
         <v>0.72</v>
@@ -22225,7 +22255,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="230" spans="1:31">
+    <row r="230" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -22236,7 +22266,7 @@
         <v>1.77</v>
       </c>
       <c r="D230">
-        <v>87.45999999999999</v>
+        <v>87.46</v>
       </c>
       <c r="E230">
         <v>144.12</v>
@@ -22278,10 +22308,10 @@
         <v>166586</v>
       </c>
       <c r="R230">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="S230">
-        <v>85.68000000000001</v>
+        <v>85.68</v>
       </c>
       <c r="T230">
         <v>54.76</v>
@@ -22290,7 +22320,7 @@
         <v>0</v>
       </c>
       <c r="V230">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="W230">
         <v>0.44</v>
@@ -22320,7 +22350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:31">
+    <row r="231" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -22415,7 +22445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:31">
+    <row r="232" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -22429,7 +22459,7 @@
         <v>92.52</v>
       </c>
       <c r="E232">
-        <v>150.08</v>
+        <v>150.08000000000001</v>
       </c>
       <c r="F232">
         <v>0</v>
@@ -22495,7 +22525,7 @@
         <v>0</v>
       </c>
       <c r="AA232">
-        <v>722.9400000000001</v>
+        <v>722.94</v>
       </c>
       <c r="AB232">
         <v>370.22</v>
@@ -22510,7 +22540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="233" spans="1:31">
+    <row r="233" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -22548,7 +22578,7 @@
         <v>922.09</v>
       </c>
       <c r="M233">
-        <v>584.2</v>
+        <v>584.20000000000005</v>
       </c>
       <c r="N233" t="s">
         <v>31</v>
@@ -22605,7 +22635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:31">
+    <row r="234" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -22619,7 +22649,7 @@
         <v>68.47</v>
       </c>
       <c r="E234">
-        <v>140.67</v>
+        <v>140.66999999999999</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -22640,7 +22670,7 @@
         <v>0</v>
       </c>
       <c r="L234">
-        <v>1029.4</v>
+        <v>1029.4000000000001</v>
       </c>
       <c r="M234">
         <v>273.7</v>
@@ -22670,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="V234">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="W234">
         <v>0.43</v>
@@ -22700,7 +22730,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="235" spans="1:31">
+    <row r="235" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -22795,7 +22825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:31">
+    <row r="236" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>234</v>
       </c>
@@ -22890,7 +22920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:31">
+    <row r="237" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -22985,7 +23015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:31">
+    <row r="238" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -23080,7 +23110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:31">
+    <row r="239" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -23094,13 +23124,13 @@
         <v>94.61</v>
       </c>
       <c r="E239">
-        <v>149.61</v>
+        <v>149.61000000000001</v>
       </c>
       <c r="F239">
         <v>0</v>
       </c>
       <c r="G239">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H239">
         <v>0.71</v>
@@ -23175,7 +23205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:31">
+    <row r="240" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>238</v>
       </c>
@@ -23183,13 +23213,13 @@
         <v>137714</v>
       </c>
       <c r="C240">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D240">
         <v>70.78</v>
       </c>
       <c r="E240">
-        <v>80.76000000000001</v>
+        <v>80.760000000000005</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -23234,7 +23264,7 @@
         <v>62.65</v>
       </c>
       <c r="T240">
-        <v>36.13</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="U240">
         <v>0</v>
@@ -23243,7 +23273,7 @@
         <v>0.42</v>
       </c>
       <c r="W240">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X240">
         <v>0</v>
@@ -23255,7 +23285,7 @@
         <v>0</v>
       </c>
       <c r="AA240">
-        <v>1308.11</v>
+        <v>1308.1099999999999</v>
       </c>
       <c r="AB240">
         <v>479.82</v>
@@ -23270,7 +23300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:31">
+    <row r="241" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -23365,7 +23395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:31">
+    <row r="242" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -23400,7 +23430,7 @@
         <v>0</v>
       </c>
       <c r="L242">
-        <v>1243.35</v>
+        <v>1243.3499999999999</v>
       </c>
       <c r="M242">
         <v>718.9</v>
@@ -23424,7 +23454,7 @@
         <v>88.47</v>
       </c>
       <c r="T242">
-        <v>72.15000000000001</v>
+        <v>72.150000000000006</v>
       </c>
       <c r="U242">
         <v>0</v>
@@ -23460,7 +23490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:31">
+    <row r="243" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -23474,7 +23504,7 @@
         <v>45.34</v>
       </c>
       <c r="E243">
-        <v>94.48999999999999</v>
+        <v>94.49</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -23555,7 +23585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:31">
+    <row r="244" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -23578,7 +23608,7 @@
         <v>0.45</v>
       </c>
       <c r="H244">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I244">
         <v>0</v>
@@ -23635,7 +23665,7 @@
         <v>0</v>
       </c>
       <c r="AA244">
-        <v>679.9299999999999</v>
+        <v>679.93</v>
       </c>
       <c r="AB244">
         <v>598.79</v>
@@ -23650,7 +23680,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245" spans="1:31">
+    <row r="245" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -23718,7 +23748,7 @@
         <v>0.45</v>
       </c>
       <c r="W245">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X245">
         <v>0</v>
@@ -23730,7 +23760,7 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>737.4299999999999</v>
+        <v>737.43</v>
       </c>
       <c r="AB245">
         <v>337.2</v>
@@ -23745,7 +23775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:31">
+    <row r="246" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -23810,7 +23840,7 @@
         <v>0</v>
       </c>
       <c r="V246">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W246">
         <v>0.71</v>
@@ -23828,7 +23858,7 @@
         <v>1044.08</v>
       </c>
       <c r="AB246">
-        <v>772.0700000000001</v>
+        <v>772.07</v>
       </c>
       <c r="AC246" t="s">
         <v>31</v>
@@ -23840,7 +23870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="247" spans="1:31">
+    <row r="247" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -23851,10 +23881,10 @@
         <v>3.84</v>
       </c>
       <c r="D247">
-        <v>71.98999999999999</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="E247">
-        <v>130.73</v>
+        <v>130.72999999999999</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -23908,7 +23938,7 @@
         <v>0.42</v>
       </c>
       <c r="W247">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X247">
         <v>0</v>
@@ -23935,7 +23965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:31">
+    <row r="248" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -23949,7 +23979,7 @@
         <v>59.57</v>
       </c>
       <c r="E248">
-        <v>134.55</v>
+        <v>134.55000000000001</v>
       </c>
       <c r="F248">
         <v>0</v>
@@ -23973,7 +24003,7 @@
         <v>484.45</v>
       </c>
       <c r="M248">
-        <v>561.6799999999999</v>
+        <v>561.67999999999995</v>
       </c>
       <c r="N248" t="s">
         <v>31</v>
@@ -24000,7 +24030,7 @@
         <v>0</v>
       </c>
       <c r="V248">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W248">
         <v>0.72</v>
@@ -24030,7 +24060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="249" spans="1:31">
+    <row r="249" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -24044,7 +24074,7 @@
         <v>70.08</v>
       </c>
       <c r="E249">
-        <v>142.39</v>
+        <v>142.38999999999999</v>
       </c>
       <c r="F249">
         <v>0</v>
@@ -24125,7 +24155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:31">
+    <row r="250" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -24136,7 +24166,7 @@
         <v>3.61</v>
       </c>
       <c r="D250">
-        <v>99.81999999999999</v>
+        <v>99.82</v>
       </c>
       <c r="E250">
         <v>124.84</v>
@@ -24220,7 +24250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:31">
+    <row r="251" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -24315,7 +24345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:31">
+    <row r="252" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -24338,7 +24368,7 @@
         <v>0.42</v>
       </c>
       <c r="H252">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I252">
         <v>0</v>
@@ -24410,7 +24440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:31">
+    <row r="253" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -24421,7 +24451,7 @@
         <v>2.04</v>
       </c>
       <c r="D253">
-        <v>97.73999999999999</v>
+        <v>97.74</v>
       </c>
       <c r="E253">
         <v>149.21</v>
@@ -24430,7 +24460,7 @@
         <v>0</v>
       </c>
       <c r="G253">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H253">
         <v>0.86</v>
@@ -24505,7 +24535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:31">
+    <row r="254" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -24585,7 +24615,7 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>1200.89</v>
+        <v>1200.8900000000001</v>
       </c>
       <c r="AB254">
         <v>610.34</v>
@@ -24600,7 +24630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:31">
+    <row r="255" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -24611,7 +24641,7 @@
         <v>1.59</v>
       </c>
       <c r="D255">
-        <v>74.29000000000001</v>
+        <v>74.290000000000006</v>
       </c>
       <c r="E255">
         <v>111.88</v>
@@ -24635,10 +24665,10 @@
         <v>0</v>
       </c>
       <c r="L255">
-        <v>888.9299999999999</v>
+        <v>888.93</v>
       </c>
       <c r="M255">
-        <v>550.08</v>
+        <v>550.08000000000004</v>
       </c>
       <c r="N255" t="s">
         <v>31</v>
@@ -24683,7 +24713,7 @@
         <v>886.37</v>
       </c>
       <c r="AB255">
-        <v>546.6799999999999</v>
+        <v>546.67999999999995</v>
       </c>
       <c r="AC255" t="s">
         <v>31</v>
@@ -24695,7 +24725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:31">
+    <row r="256" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -24703,7 +24733,7 @@
         <v>155187</v>
       </c>
       <c r="C256">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="D256">
         <v>59.86</v>
@@ -24733,7 +24763,7 @@
         <v>187.46</v>
       </c>
       <c r="M256">
-        <v>665.4400000000001</v>
+        <v>665.44</v>
       </c>
       <c r="N256" t="s">
         <v>31</v>
@@ -24748,7 +24778,7 @@
         <v>121986</v>
       </c>
       <c r="R256">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="S256">
         <v>58.53</v>
@@ -24760,7 +24790,7 @@
         <v>0</v>
       </c>
       <c r="V256">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="W256">
         <v>0.45</v>
@@ -24790,7 +24820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:31">
+    <row r="257" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>255</v>
       </c>
@@ -24885,7 +24915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:31">
+    <row r="258" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>256</v>
       </c>
@@ -24896,7 +24926,7 @@
         <v>3.34</v>
       </c>
       <c r="D258">
-        <v>90.59999999999999</v>
+        <v>90.6</v>
       </c>
       <c r="E258">
         <v>126.53</v>
@@ -24908,7 +24938,7 @@
         <v>0.31</v>
       </c>
       <c r="H258">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I258">
         <v>0</v>
@@ -24941,7 +24971,7 @@
         <v>3.33</v>
       </c>
       <c r="S258">
-        <v>86.90000000000001</v>
+        <v>86.9</v>
       </c>
       <c r="T258">
         <v>77.3</v>
@@ -24965,7 +24995,7 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>514.55</v>
+        <v>514.54999999999995</v>
       </c>
       <c r="AB258">
         <v>505.17</v>
@@ -24980,7 +25010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:31">
+    <row r="259" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>257</v>
       </c>
@@ -24991,7 +25021,7 @@
         <v>1.83</v>
       </c>
       <c r="D259">
-        <v>89.73999999999999</v>
+        <v>89.74</v>
       </c>
       <c r="E259">
         <v>110.77</v>
@@ -25015,7 +25045,7 @@
         <v>0</v>
       </c>
       <c r="L259">
-        <v>693.3200000000001</v>
+        <v>693.32</v>
       </c>
       <c r="M259">
         <v>767.24</v>
@@ -25036,7 +25066,7 @@
         <v>2</v>
       </c>
       <c r="S259">
-        <v>90.93000000000001</v>
+        <v>90.93</v>
       </c>
       <c r="T259">
         <v>68.13</v>
@@ -25063,7 +25093,7 @@
         <v>702.78</v>
       </c>
       <c r="AB259">
-        <v>769.5599999999999</v>
+        <v>769.56</v>
       </c>
       <c r="AC259" t="s">
         <v>31</v>
@@ -25075,7 +25105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="260" spans="1:31">
+    <row r="260" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>258</v>
       </c>
@@ -25098,7 +25128,7 @@
         <v>0.44</v>
       </c>
       <c r="H260">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -25113,7 +25143,7 @@
         <v>365.03</v>
       </c>
       <c r="M260">
-        <v>513.9299999999999</v>
+        <v>513.92999999999995</v>
       </c>
       <c r="N260" t="s">
         <v>31</v>
@@ -25134,7 +25164,7 @@
         <v>59.32</v>
       </c>
       <c r="T260">
-        <v>65.15000000000001</v>
+        <v>65.150000000000006</v>
       </c>
       <c r="U260">
         <v>0</v>
@@ -25143,7 +25173,7 @@
         <v>0.42</v>
       </c>
       <c r="W260">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X260">
         <v>0</v>
@@ -25170,7 +25200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:31">
+    <row r="261" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>259</v>
       </c>
@@ -25184,7 +25214,7 @@
         <v>69.47</v>
       </c>
       <c r="E261">
-        <v>151.61</v>
+        <v>151.61000000000001</v>
       </c>
       <c r="F261">
         <v>0</v>
@@ -25205,7 +25235,7 @@
         <v>0</v>
       </c>
       <c r="L261">
-        <v>631.92</v>
+        <v>631.91999999999996</v>
       </c>
       <c r="M261">
         <v>352.56</v>
@@ -25229,13 +25259,13 @@
         <v>71.69</v>
       </c>
       <c r="T261">
-        <v>94.04000000000001</v>
+        <v>94.04</v>
       </c>
       <c r="U261">
         <v>0</v>
       </c>
       <c r="V261">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="W261">
         <v>0.45</v>
@@ -25250,7 +25280,7 @@
         <v>0</v>
       </c>
       <c r="AA261">
-        <v>630.55</v>
+        <v>630.54999999999995</v>
       </c>
       <c r="AB261">
         <v>346.56</v>
@@ -25265,7 +25295,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:31">
+    <row r="262" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>260</v>
       </c>
@@ -25360,7 +25390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="263" spans="1:31">
+    <row r="263" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>261</v>
       </c>
@@ -25455,7 +25485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:31">
+    <row r="264" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>262</v>
       </c>
@@ -25475,7 +25505,7 @@
         <v>0</v>
       </c>
       <c r="G264">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H264">
         <v>0.44</v>
@@ -25490,10 +25520,10 @@
         <v>0</v>
       </c>
       <c r="L264">
-        <v>932.5700000000001</v>
+        <v>932.57</v>
       </c>
       <c r="M264">
-        <v>567.0700000000001</v>
+        <v>567.07000000000005</v>
       </c>
       <c r="N264" t="s">
         <v>31</v>
@@ -25511,7 +25541,7 @@
         <v>3.36</v>
       </c>
       <c r="S264">
-        <v>79.43000000000001</v>
+        <v>79.430000000000007</v>
       </c>
       <c r="T264">
         <v>99.11</v>
@@ -25550,7 +25580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="265" spans="1:31">
+    <row r="265" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>263</v>
       </c>
@@ -25561,7 +25591,7 @@
         <v>1.91</v>
       </c>
       <c r="D265">
-        <v>81.73999999999999</v>
+        <v>81.739999999999995</v>
       </c>
       <c r="E265">
         <v>155.91</v>
@@ -25630,7 +25660,7 @@
         <v>0</v>
       </c>
       <c r="AA265">
-        <v>1257.66</v>
+        <v>1257.6600000000001</v>
       </c>
       <c r="AB265">
         <v>397.08</v>
@@ -25645,7 +25675,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:31">
+    <row r="266" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>264</v>
       </c>
@@ -25659,7 +25689,7 @@
         <v>40.42</v>
       </c>
       <c r="E266">
-        <v>92.01000000000001</v>
+        <v>92.01</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -25683,7 +25713,7 @@
         <v>1309.21</v>
       </c>
       <c r="M266">
-        <v>820.4299999999999</v>
+        <v>820.43</v>
       </c>
       <c r="N266" t="s">
         <v>31</v>
@@ -25704,7 +25734,7 @@
         <v>48.78</v>
       </c>
       <c r="T266">
-        <v>39.16</v>
+        <v>39.159999999999997</v>
       </c>
       <c r="U266">
         <v>0</v>
@@ -25728,7 +25758,7 @@
         <v>1229.78</v>
       </c>
       <c r="AB266">
-        <v>809.3099999999999</v>
+        <v>809.31</v>
       </c>
       <c r="AC266" t="s">
         <v>31</v>
@@ -25740,7 +25770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="267" spans="1:31">
+    <row r="267" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>265</v>
       </c>
@@ -25748,13 +25778,13 @@
         <v>136908</v>
       </c>
       <c r="C267">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="D267">
         <v>71.17</v>
       </c>
       <c r="E267">
-        <v>133.11</v>
+        <v>133.11000000000001</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -25796,7 +25826,7 @@
         <v>2.19</v>
       </c>
       <c r="S267">
-        <v>72.56999999999999</v>
+        <v>72.569999999999993</v>
       </c>
       <c r="T267">
         <v>65.94</v>
@@ -25820,7 +25850,7 @@
         <v>0</v>
       </c>
       <c r="AA267">
-        <v>522.08</v>
+        <v>522.08000000000004</v>
       </c>
       <c r="AB267">
         <v>596.6</v>
@@ -25835,7 +25865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:31">
+    <row r="268" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>266</v>
       </c>
@@ -25894,7 +25924,7 @@
         <v>115.16</v>
       </c>
       <c r="T268">
-        <v>93.76000000000001</v>
+        <v>93.76</v>
       </c>
       <c r="U268">
         <v>0</v>
@@ -25930,7 +25960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:31">
+    <row r="269" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>267</v>
       </c>
@@ -25941,10 +25971,10 @@
         <v>2.61</v>
       </c>
       <c r="D269">
-        <v>64.45999999999999</v>
+        <v>64.459999999999994</v>
       </c>
       <c r="E269">
-        <v>95.26000000000001</v>
+        <v>95.26</v>
       </c>
       <c r="F269">
         <v>0</v>
@@ -26013,7 +26043,7 @@
         <v>842.83</v>
       </c>
       <c r="AB269">
-        <v>867.0700000000001</v>
+        <v>867.07</v>
       </c>
       <c r="AC269" t="s">
         <v>31</v>
@@ -26025,7 +26055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="270" spans="1:31">
+    <row r="270" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>268</v>
       </c>
@@ -26048,7 +26078,7 @@
         <v>0.71</v>
       </c>
       <c r="H270">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I270">
         <v>0</v>
@@ -26063,7 +26093,7 @@
         <v>183.58</v>
       </c>
       <c r="M270">
-        <v>540.1799999999999</v>
+        <v>540.17999999999995</v>
       </c>
       <c r="N270" t="s">
         <v>31</v>
@@ -26120,7 +26150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:31">
+    <row r="271" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>269</v>
       </c>
@@ -26176,7 +26206,7 @@
         <v>1.59</v>
       </c>
       <c r="S271">
-        <v>74.06999999999999</v>
+        <v>74.069999999999993</v>
       </c>
       <c r="T271">
         <v>81.77</v>
@@ -26215,7 +26245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:31">
+    <row r="272" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -26226,7 +26256,7 @@
         <v>1.68</v>
       </c>
       <c r="D272">
-        <v>85.65000000000001</v>
+        <v>85.65</v>
       </c>
       <c r="E272">
         <v>133.41</v>
@@ -26310,7 +26340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:31">
+    <row r="273" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>271</v>
       </c>
@@ -26363,7 +26393,7 @@
         <v>169559</v>
       </c>
       <c r="R273">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="S273">
         <v>85.22</v>
@@ -26405,7 +26435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="274" spans="1:31">
+    <row r="274" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>272</v>
       </c>
@@ -26461,10 +26491,10 @@
         <v>2.09</v>
       </c>
       <c r="S274">
-        <v>95.70999999999999</v>
+        <v>95.71</v>
       </c>
       <c r="T274">
-        <v>67.31999999999999</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="U274">
         <v>0</v>
@@ -26500,7 +26530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:31">
+    <row r="275" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>273</v>
       </c>
@@ -26511,7 +26541,7 @@
         <v>3.16</v>
       </c>
       <c r="D275">
-        <v>68.65000000000001</v>
+        <v>68.650000000000006</v>
       </c>
       <c r="E275">
         <v>75.78</v>
@@ -26556,10 +26586,10 @@
         <v>3.19</v>
       </c>
       <c r="S275">
-        <v>68.43000000000001</v>
+        <v>68.430000000000007</v>
       </c>
       <c r="T275">
-        <v>36.48</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="U275">
         <v>0</v>
@@ -26595,7 +26625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="276" spans="1:31">
+    <row r="276" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>274</v>
       </c>
@@ -26663,7 +26693,7 @@
         <v>0.31</v>
       </c>
       <c r="W276">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X276">
         <v>0</v>
@@ -26690,7 +26720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:31">
+    <row r="277" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>275</v>
       </c>
@@ -26698,7 +26728,7 @@
         <v>91228</v>
       </c>
       <c r="C277">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="D277">
         <v>80.06</v>
@@ -26743,7 +26773,7 @@
         <v>79636</v>
       </c>
       <c r="R277">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="S277">
         <v>75.83</v>
@@ -26785,7 +26815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="278" spans="1:31">
+    <row r="278" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>276</v>
       </c>
@@ -26808,7 +26838,7 @@
         <v>0.42</v>
       </c>
       <c r="H278">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I278">
         <v>0</v>
@@ -26880,7 +26910,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="279" spans="1:31">
+    <row r="279" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>277</v>
       </c>
@@ -26900,7 +26930,7 @@
         <v>0</v>
       </c>
       <c r="G279">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H279">
         <v>0.71</v>
@@ -26975,7 +27005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="1:31">
+    <row r="280" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>278</v>
       </c>
@@ -26983,7 +27013,7 @@
         <v>113711</v>
       </c>
       <c r="C280">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="D280">
         <v>70.61</v>
@@ -27010,7 +27040,7 @@
         <v>0</v>
       </c>
       <c r="L280">
-        <v>1229.59</v>
+        <v>1229.5899999999999</v>
       </c>
       <c r="M280">
         <v>728.14</v>
@@ -27028,7 +27058,7 @@
         <v>102438</v>
       </c>
       <c r="R280">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="S280">
         <v>71.16</v>
@@ -27043,7 +27073,7 @@
         <v>0.45</v>
       </c>
       <c r="W280">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X280">
         <v>0</v>
@@ -27070,7 +27100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="281" spans="1:31">
+    <row r="281" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>279</v>
       </c>
@@ -27084,7 +27114,7 @@
         <v>35.75</v>
       </c>
       <c r="E281">
-        <v>36.2</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F281">
         <v>0</v>
@@ -27108,7 +27138,7 @@
         <v>876.89</v>
       </c>
       <c r="M281">
-        <v>937.1799999999999</v>
+        <v>937.18</v>
       </c>
       <c r="N281" t="s">
         <v>31</v>
@@ -27165,7 +27195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:31">
+    <row r="282" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>280</v>
       </c>
@@ -27218,7 +27248,7 @@
         <v>146696</v>
       </c>
       <c r="R282">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="S282">
         <v>86.62</v>
@@ -27233,7 +27263,7 @@
         <v>0.44</v>
       </c>
       <c r="W282">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X282">
         <v>0</v>
@@ -27260,7 +27290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:31">
+    <row r="283" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>281</v>
       </c>
@@ -27271,7 +27301,7 @@
         <v>3.92</v>
       </c>
       <c r="D283">
-        <v>97.68000000000001</v>
+        <v>97.68</v>
       </c>
       <c r="E283">
         <v>99.73</v>
@@ -27316,7 +27346,7 @@
         <v>4.21</v>
       </c>
       <c r="S283">
-        <v>97.15000000000001</v>
+        <v>97.15</v>
       </c>
       <c r="T283">
         <v>58.52</v>
@@ -27355,7 +27385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="284" spans="1:31">
+    <row r="284" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>282</v>
       </c>
@@ -27369,7 +27399,7 @@
         <v>63.32</v>
       </c>
       <c r="E284">
-        <v>93.95999999999999</v>
+        <v>93.96</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -27393,7 +27423,7 @@
         <v>481.48</v>
       </c>
       <c r="M284">
-        <v>265.65</v>
+        <v>265.64999999999998</v>
       </c>
       <c r="N284" t="s">
         <v>31</v>
@@ -27450,7 +27480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:31">
+    <row r="285" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>283</v>
       </c>
@@ -27470,7 +27500,7 @@
         <v>0</v>
       </c>
       <c r="G285">
-        <v>0.5600000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H285">
         <v>0.44</v>
@@ -27545,7 +27575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:31">
+    <row r="286" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>284</v>
       </c>
@@ -27640,7 +27670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:31">
+    <row r="287" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>285</v>
       </c>
@@ -27735,7 +27765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="288" spans="1:31">
+    <row r="288" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>286</v>
       </c>
@@ -27746,7 +27776,7 @@
         <v>2.19</v>
       </c>
       <c r="D288">
-        <v>99.26000000000001</v>
+        <v>99.26</v>
       </c>
       <c r="E288">
         <v>122.97</v>
@@ -27770,7 +27800,7 @@
         <v>0</v>
       </c>
       <c r="L288">
-        <v>1109.89</v>
+        <v>1109.8900000000001</v>
       </c>
       <c r="M288">
         <v>291.31</v>
@@ -27830,7 +27860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:31">
+    <row r="289" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>287</v>
       </c>
@@ -27925,7 +27955,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="290" spans="1:31">
+    <row r="290" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>288</v>
       </c>
@@ -27978,13 +28008,13 @@
         <v>105185</v>
       </c>
       <c r="R290">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="S290">
         <v>81.33</v>
       </c>
       <c r="T290">
-        <v>35.88</v>
+        <v>35.880000000000003</v>
       </c>
       <c r="U290">
         <v>0</v>
@@ -28020,7 +28050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="291" spans="1:31">
+    <row r="291" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>289</v>
       </c>
@@ -28115,7 +28145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:31">
+    <row r="292" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>290</v>
       </c>
@@ -28138,7 +28168,7 @@
         <v>0.71</v>
       </c>
       <c r="H292">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I292">
         <v>0</v>
@@ -28210,7 +28240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="293" spans="1:31">
+    <row r="293" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>291</v>
       </c>
@@ -28248,7 +28278,7 @@
         <v>572.65</v>
       </c>
       <c r="M293">
-        <v>326.16</v>
+        <v>326.16000000000003</v>
       </c>
       <c r="N293" t="s">
         <v>31</v>
@@ -28305,7 +28335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:31">
+    <row r="294" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>292</v>
       </c>
@@ -28343,7 +28373,7 @@
         <v>323.19</v>
       </c>
       <c r="M294">
-        <v>628.3200000000001</v>
+        <v>628.32000000000005</v>
       </c>
       <c r="N294" t="s">
         <v>30</v>
@@ -28400,7 +28430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:31">
+    <row r="295" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>293</v>
       </c>
@@ -28414,7 +28444,7 @@
         <v>96.64</v>
       </c>
       <c r="E295">
-        <v>139.36</v>
+        <v>139.36000000000001</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -28480,7 +28510,7 @@
         <v>0</v>
       </c>
       <c r="AA295">
-        <v>531.95</v>
+        <v>531.95000000000005</v>
       </c>
       <c r="AB295">
         <v>347.73</v>
@@ -28495,7 +28525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="296" spans="1:31">
+    <row r="296" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>294</v>
       </c>
@@ -28503,7 +28533,7 @@
         <v>31617</v>
       </c>
       <c r="C296">
-        <v>8.640000000000001</v>
+        <v>8.64</v>
       </c>
       <c r="D296">
         <v>113.31</v>
@@ -28530,10 +28560,10 @@
         <v>0</v>
       </c>
       <c r="L296">
-        <v>532.17</v>
+        <v>532.16999999999996</v>
       </c>
       <c r="M296">
-        <v>652.8</v>
+        <v>652.79999999999995</v>
       </c>
       <c r="N296" t="s">
         <v>30</v>
@@ -28590,7 +28620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="297" spans="1:31">
+    <row r="297" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>295</v>
       </c>
@@ -28604,13 +28634,13 @@
         <v>100.43</v>
       </c>
       <c r="E297">
-        <v>97.59999999999999</v>
+        <v>97.6</v>
       </c>
       <c r="F297">
         <v>0</v>
       </c>
       <c r="G297">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H297">
         <v>0.19</v>
@@ -28646,7 +28676,7 @@
         <v>2.99</v>
       </c>
       <c r="S297">
-        <v>93.93000000000001</v>
+        <v>93.93</v>
       </c>
       <c r="T297">
         <v>44.79</v>
@@ -28685,7 +28715,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:31">
+    <row r="298" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>296</v>
       </c>
@@ -28693,10 +28723,10 @@
         <v>41198</v>
       </c>
       <c r="C298">
-        <v>4.61</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D298">
-        <v>82.54000000000001</v>
+        <v>82.54</v>
       </c>
       <c r="E298">
         <v>132.18</v>
@@ -28744,7 +28774,7 @@
         <v>80.8</v>
       </c>
       <c r="T298">
-        <v>64.09999999999999</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="U298">
         <v>0</v>
@@ -28780,7 +28810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="1:31">
+    <row r="299" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>297</v>
       </c>
@@ -28863,7 +28893,7 @@
         <v>930.17</v>
       </c>
       <c r="AB299">
-        <v>766.3099999999999</v>
+        <v>766.31</v>
       </c>
       <c r="AC299" t="s">
         <v>30</v>
@@ -28875,7 +28905,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:31">
+    <row r="300" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>298</v>
       </c>
@@ -28895,7 +28925,7 @@
         <v>0</v>
       </c>
       <c r="G300">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H300">
         <v>0.06</v>
@@ -28910,7 +28940,7 @@
         <v>0</v>
       </c>
       <c r="L300">
-        <v>1091.14</v>
+        <v>1091.1400000000001</v>
       </c>
       <c r="M300">
         <v>467.49</v>
@@ -28934,7 +28964,7 @@
         <v>37.28</v>
       </c>
       <c r="T300">
-        <v>39.62</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="U300">
         <v>0</v>
@@ -28970,7 +29000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="1:31">
+    <row r="301" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>299</v>
       </c>
@@ -29065,7 +29095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:31">
+    <row r="302" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>300</v>
       </c>
@@ -29076,7 +29106,7 @@
         <v>5.24</v>
       </c>
       <c r="D302">
-        <v>71.81999999999999</v>
+        <v>71.819999999999993</v>
       </c>
       <c r="E302">
         <v>111.29</v>
@@ -29088,7 +29118,7 @@
         <v>0.86</v>
       </c>
       <c r="H302">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I302">
         <v>0</v>
@@ -29103,7 +29133,7 @@
         <v>671.52</v>
       </c>
       <c r="M302">
-        <v>781.1799999999999</v>
+        <v>781.18</v>
       </c>
       <c r="N302" t="s">
         <v>30</v>
@@ -29160,7 +29190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="303" spans="1:31">
+    <row r="303" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>301</v>
       </c>
@@ -29255,7 +29285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:31">
+    <row r="304" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>302</v>
       </c>
@@ -29350,7 +29380,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="305" spans="1:31">
+    <row r="305" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>303</v>
       </c>
@@ -29361,10 +29391,10 @@
         <v>3.54</v>
       </c>
       <c r="D305">
-        <v>68.20999999999999</v>
+        <v>68.209999999999994</v>
       </c>
       <c r="E305">
-        <v>147.98</v>
+        <v>147.97999999999999</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -29430,7 +29460,7 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>941.5700000000001</v>
+        <v>941.57</v>
       </c>
       <c r="AB305">
         <v>351.46</v>
